--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -1,148 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587A52E2-F13C-49AD-9ED9-261E0359FCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="14620" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>demo.Quality</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COMMON</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RARE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPIC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>精良</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="9" tint="0.7999511703848384"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -165,39 +68,145 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -458,146 +467,281 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col width="19" customWidth="1" style="4" min="2" max="2"/>
+    <col width="20.875" customWidth="1" style="4" min="3" max="3"/>
+    <col width="14.125" customWidth="1" style="4" min="4" max="5"/>
+    <col width="9.375" customWidth="1" style="4" min="6" max="6"/>
+    <col width="5" customWidth="1" style="4" min="7" max="7"/>
+    <col width="13.5" customWidth="1" style="4" min="8" max="8"/>
+    <col width="5.25" customWidth="1" style="4" min="9" max="9"/>
+    <col width="12.125" customWidth="1" style="4" min="10" max="10"/>
+    <col width="15.125" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" s="4">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>demo.Quality</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>COMMON</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>精良</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>EPIC</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>demo.BallType</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="b">
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>demo.TileStateType</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D9" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Mud</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>泥浆</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="127">
   <si>
     <t>##var</t>
   </si>
@@ -143,10 +143,16 @@
     <t>湿土</t>
   </si>
   <si>
-    <t>EarthSand</t>
-  </si>
-  <si>
-    <t>沙土</t>
+    <t>Sand</t>
+  </si>
+  <si>
+    <t>沙</t>
+  </si>
+  <si>
+    <t>Clay</t>
+  </si>
+  <si>
+    <t>粘土</t>
   </si>
   <si>
     <t>SeedIce</t>
@@ -173,75 +179,63 @@
     <t>电种子</t>
   </si>
   <si>
+    <t>demo.ElementTag</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>Soil</t>
+  </si>
+  <si>
+    <t>含土</t>
+  </si>
+  <si>
+    <t>含沙</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>含植物</t>
+  </si>
+  <si>
+    <t>demo.ElementType</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>土</t>
+  </si>
+  <si>
+    <t>Seed</t>
+  </si>
+  <si>
+    <t>地形种子</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>地形</t>
+  </si>
+  <si>
     <t>demo.TileStateType</t>
   </si>
   <si>
     <t>Normal</t>
   </si>
   <si>
-    <t>常规</t>
+    <t>空地</t>
   </si>
   <si>
     <t>Mud</t>
   </si>
   <si>
-    <t>泥浆</t>
-  </si>
-  <si>
-    <t>demo.ElementTag</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>Soil</t>
-  </si>
-  <si>
-    <t>含土</t>
-  </si>
-  <si>
-    <t>Sand</t>
-  </si>
-  <si>
-    <t>含沙</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>含植物</t>
-  </si>
-  <si>
-    <t>demo.ElementType</t>
-  </si>
-  <si>
-    <t>水</t>
-  </si>
-  <si>
-    <t>土</t>
-  </si>
-  <si>
-    <t>Seed</t>
-  </si>
-  <si>
-    <t>地形种子</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>地形</t>
-  </si>
-  <si>
-    <t>demo.TileType</t>
-  </si>
-  <si>
-    <t>空地</t>
-  </si>
-  <si>
     <t>普通泥浆</t>
   </si>
   <si>
@@ -345,6 +339,75 @@
   </si>
   <si>
     <t>基础植物区</t>
+  </si>
+  <si>
+    <t>demo.TileEffectType</t>
+  </si>
+  <si>
+    <t>Slow</t>
+  </si>
+  <si>
+    <t>减速</t>
+  </si>
+  <si>
+    <t>Skid</t>
+  </si>
+  <si>
+    <t>打滑</t>
+  </si>
+  <si>
+    <t>Slid</t>
+  </si>
+  <si>
+    <t>滑行</t>
+  </si>
+  <si>
+    <t>KnockBack</t>
+  </si>
+  <si>
+    <t>击退</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>阻挡</t>
+  </si>
+  <si>
+    <t>Numbness</t>
+  </si>
+  <si>
+    <t>麻痹</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>定身</t>
+  </si>
+  <si>
+    <t>DamageInstant</t>
+  </si>
+  <si>
+    <t>瞬时伤害</t>
+  </si>
+  <si>
+    <t>DamageOverTime</t>
+  </si>
+  <si>
+    <t>持续伤害</t>
+  </si>
+  <si>
+    <t>InheritedTW</t>
+  </si>
+  <si>
+    <t>温湿度继承</t>
+  </si>
+  <si>
+    <t>ClearPlant</t>
+  </si>
+  <si>
+    <t>清除植物</t>
   </si>
 </sst>
 </file>
@@ -357,10 +420,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -880,137 +949,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1024,13 +1093,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1351,7 +1426,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
@@ -1360,7 +1435,7 @@
     <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.3333333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
   </cols>
@@ -1390,10 +1465,10 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1500,7 +1575,7 @@
       <c r="H7" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1511,7 +1586,7 @@
       <c r="H8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1522,7 +1597,7 @@
       <c r="H9" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1533,7 +1608,7 @@
       <c r="H10" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1544,7 +1619,7 @@
       <c r="H11" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="8" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1555,7 +1630,7 @@
       <c r="H12" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="8" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1566,7 +1641,7 @@
       <c r="H13" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="8" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1577,7 +1652,7 @@
       <c r="H14" t="s">
         <v>42</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="8" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1588,7 +1663,7 @@
       <c r="H15" t="s">
         <v>44</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1599,294 +1674,387 @@
       <c r="H16" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="17" spans="2:9">
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="H17" t="s">
         <v>48</v>
       </c>
-      <c r="C17" t="b">
+      <c r="I17" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="1">
         <v>0</v>
       </c>
-      <c r="D17" t="b">
+    </row>
+    <row r="19" spans="8:10">
+      <c r="H19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="1">
         <v>1</v>
-      </c>
-      <c r="H17" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="20" spans="8:10">
       <c r="H20" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="8:10">
       <c r="H21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="C22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="8:10">
-      <c r="H22" s="1" t="s">
+    </row>
+    <row r="23" spans="8:9">
+      <c r="H23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J22" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="24" spans="8:9">
       <c r="H24" s="1" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="8:9">
       <c r="H25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="C26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="8:9">
+      <c r="H27" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="26" spans="8:9">
-      <c r="H26" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="28" spans="8:9">
       <c r="H28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="8:9">
       <c r="H29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="8:9">
       <c r="H30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="8:9">
       <c r="H31" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="8:9">
       <c r="H32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="8:9">
       <c r="H33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="8:9">
       <c r="H34" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="8:9">
       <c r="H35" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="8:9">
       <c r="H36" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="8:9">
       <c r="H37" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="8:9">
       <c r="H38" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="8:9">
       <c r="H39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="8:9">
       <c r="H40" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="8:9">
       <c r="H41" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="8:9">
       <c r="H42" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="8:9">
       <c r="H43" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="8:9">
       <c r="H44" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="8:9">
       <c r="H45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="C46" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="8:9">
+      <c r="H47" s="1" t="s">
         <v>105</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="8:9">
+      <c r="H48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="8:9">
+      <c r="H49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="8:9">
+      <c r="H50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="8:9">
+      <c r="H51" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="8:9">
+      <c r="H52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" spans="8:9">
+      <c r="H53" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="8:9">
+      <c r="H54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="8:9">
+      <c r="H55" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="8:9">
+      <c r="H56" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="57" spans="8:9">
+      <c r="H57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -86,7 +86,7 @@
     <t>注释</t>
   </si>
   <si>
-    <t>demo.Quality</t>
+    <t>dso.Quality</t>
   </si>
   <si>
     <t>COMMON</t>
@@ -110,7 +110,7 @@
     <t/>
   </si>
   <si>
-    <t>demo.BallType</t>
+    <t>dso.BallType</t>
   </si>
   <si>
     <t>Water</t>
@@ -179,7 +179,7 @@
     <t>电种子</t>
   </si>
   <si>
-    <t>demo.ElementTag</t>
+    <t>dso.ElementTag</t>
   </si>
   <si>
     <t>None</t>
@@ -203,7 +203,7 @@
     <t>含植物</t>
   </si>
   <si>
-    <t>demo.ElementType</t>
+    <t>dso.ElementType</t>
   </si>
   <si>
     <t>水</t>
@@ -224,7 +224,7 @@
     <t>地形</t>
   </si>
   <si>
-    <t>demo.TileStateType</t>
+    <t>dso.TileStateType</t>
   </si>
   <si>
     <t>Normal</t>
@@ -341,7 +341,7 @@
     <t>基础植物区</t>
   </si>
   <si>
-    <t>demo.TileEffectType</t>
+    <t>dso.TileEffectType</t>
   </si>
   <si>
     <t>Slow</t>

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>##var</t>
   </si>
@@ -408,6 +408,60 @@
   </si>
   <si>
     <t>清除植物</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>纯土</t>
+  </si>
+  <si>
+    <t>无状态</t>
+  </si>
+  <si>
+    <t>基础水</t>
+  </si>
+  <si>
+    <t>基础土</t>
+  </si>
+  <si>
+    <t>ConductZone</t>
+  </si>
+  <si>
+    <t>导电区</t>
+  </si>
+  <si>
+    <t>FlameField</t>
+  </si>
+  <si>
+    <t>燎原火海</t>
+  </si>
+  <si>
+    <t>ChargedThorn</t>
+  </si>
+  <si>
+    <t>带电荆棘</t>
+  </si>
+  <si>
+    <t>FrostSpike</t>
+  </si>
+  <si>
+    <t>霜冻冰刺</t>
+  </si>
+  <si>
+    <t>dso.SeedType</t>
+  </si>
+  <si>
+    <t>空种子</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Elec</t>
+  </si>
+  <si>
+    <t>Ice</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1478,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1:L57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
@@ -1527,535 +1581,2083 @@
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="2:9">
+      <c r="A4"/>
       <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="b">
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4">
         <v>1</v>
       </c>
+      <c r="E4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4"/>
+      <c r="G4"/>
       <c r="H4" t="s">
         <v>20</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
       </c>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
     </row>
     <row r="5" spans="8:9">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
       <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
         <v>23</v>
       </c>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
     </row>
     <row r="6" spans="8:9">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
       <c r="H6" t="s">
         <v>24</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
       </c>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7" s="8"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8"/>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="b">
+      <c r="C8">
         <v>0</v>
       </c>
-      <c r="D7" t="b">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
+      <c r="E8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
     </row>
     <row r="9" spans="2:9">
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>33</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
     </row>
     <row r="10" spans="2:9">
+      <c r="A10"/>
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
-      <c r="H10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10" s="8"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
     </row>
     <row r="11" spans="2:9">
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
+      <c r="A11"/>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11"/>
+      <c r="G11"/>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>37</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
     </row>
     <row r="12" spans="2:9">
+      <c r="A12"/>
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>39</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
     </row>
     <row r="13" spans="2:9">
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
-      <c r="H13" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>41</v>
-      </c>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13" s="8"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
+      <c r="A14"/>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14"/>
+      <c r="G14"/>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>43</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
     </row>
     <row r="15" spans="2:9">
+      <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
       <c r="H15" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>45</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
     </row>
     <row r="16" spans="2:9">
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
       <c r="H16" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>47</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
     </row>
     <row r="17" spans="2:9">
+      <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="I17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="A18"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J18" s="1">
+        <v>5</v>
+      </c>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+    </row>
+    <row r="19" spans="8:10">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" s="1">
+        <v>6</v>
+      </c>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+    </row>
+    <row r="20" spans="8:10">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" s="1">
+        <v>8</v>
+      </c>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+    </row>
+    <row r="21" spans="8:10">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="1">
+        <v>14</v>
+      </c>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="A22"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J22">
+        <v>15</v>
+      </c>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+    </row>
+    <row r="23" spans="8:9">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J23">
+        <v>16</v>
+      </c>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+    </row>
+    <row r="24" spans="8:9">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J24">
+        <v>17</v>
+      </c>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+    </row>
+    <row r="25" spans="8:9">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J25">
+        <v>18</v>
+      </c>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="A26"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J26">
+        <v>19</v>
+      </c>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+    </row>
+    <row r="27" spans="8:9">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J27">
+        <v>20</v>
+      </c>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+    </row>
+    <row r="28" spans="8:9">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="J28">
+        <v>21</v>
+      </c>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+    </row>
+    <row r="29" spans="8:9">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="J29">
+        <v>22</v>
+      </c>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+    </row>
+    <row r="30" spans="8:9">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="J30">
+        <v>23</v>
+      </c>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+    </row>
+    <row r="31" spans="8:9">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="9"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+    </row>
+    <row r="32" spans="8:9">
+      <c r="A32"/>
+      <c r="B32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+    </row>
+    <row r="33" spans="8:9">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+    </row>
+    <row r="34" spans="8:9">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I34" s="9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="8:10">
-      <c r="H20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" s="1">
+      <c r="J34">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="8:10">
-      <c r="H21" s="1" t="s">
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+    </row>
+    <row r="35" spans="8:9">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J35">
+        <v>3</v>
+      </c>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+    </row>
+    <row r="36" spans="8:9">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J21" s="1">
+      <c r="I36" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J36">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="8:9">
-      <c r="H23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="8:9">
-      <c r="H24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="8:9">
-      <c r="H25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="8:9">
-      <c r="H27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="8:9">
-      <c r="H28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="8:9">
-      <c r="H29" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="8:9">
-      <c r="H30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="8:9">
-      <c r="H31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="8:9">
-      <c r="H32" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="8:9">
-      <c r="H33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="8:9">
-      <c r="H34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="8:9">
-      <c r="H35" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="8:9">
-      <c r="H36" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>85</v>
-      </c>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
     </row>
     <row r="37" spans="8:9">
-      <c r="H37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="9"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
     </row>
     <row r="38" spans="8:9">
-      <c r="H38" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>89</v>
-      </c>
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="9"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
     </row>
     <row r="39" spans="8:9">
-      <c r="H39" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>91</v>
-      </c>
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="9"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
     </row>
     <row r="40" spans="8:9">
-      <c r="H40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>93</v>
-      </c>
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="9"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
     </row>
     <row r="41" spans="8:9">
-      <c r="H41" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>95</v>
-      </c>
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="9"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
     </row>
     <row r="42" spans="8:9">
-      <c r="H42" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>97</v>
-      </c>
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="9"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
     </row>
     <row r="43" spans="8:9">
-      <c r="H43" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="9"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
     </row>
     <row r="44" spans="8:9">
-      <c r="H44" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>101</v>
-      </c>
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="9"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
     </row>
     <row r="45" spans="8:9">
-      <c r="H45" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>103</v>
-      </c>
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="9"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C46" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D46" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="A46"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="5"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
     </row>
     <row r="47" spans="8:9">
-      <c r="H47" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>106</v>
-      </c>
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="10"/>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
     </row>
     <row r="48" spans="8:9">
-      <c r="H48" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>108</v>
-      </c>
+      <c r="A48"/>
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="10"/>
+      <c r="J48"/>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
     </row>
     <row r="49" spans="8:9">
-      <c r="H49" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>110</v>
-      </c>
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="10"/>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
     </row>
     <row r="50" spans="8:9">
-      <c r="H50" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>112</v>
-      </c>
+      <c r="A50"/>
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="10"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+      <c r="M50"/>
     </row>
     <row r="51" spans="8:9">
-      <c r="H51" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>114</v>
-      </c>
+      <c r="A51"/>
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="10"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
     </row>
     <row r="52" spans="8:9">
-      <c r="H52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>116</v>
-      </c>
+      <c r="A52"/>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="10"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
     </row>
     <row r="53" spans="8:9">
-      <c r="H53" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>118</v>
-      </c>
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="10"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
     </row>
     <row r="54" spans="8:9">
-      <c r="H54" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>120</v>
-      </c>
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="10"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
     </row>
     <row r="55" spans="8:9">
-      <c r="H55" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>122</v>
-      </c>
+      <c r="A55"/>
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="10"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
     </row>
     <row r="56" spans="8:9">
-      <c r="H56" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>124</v>
-      </c>
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="10"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
     </row>
     <row r="57" spans="8:9">
-      <c r="H57" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I57" s="10" t="s">
-        <v>126</v>
-      </c>
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="10"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+    </row>
+    <row r="58">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
+      <c r="M58"/>
+    </row>
+    <row r="59">
+      <c r="A59"/>
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
+    </row>
+    <row r="60">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+      <c r="K60"/>
+      <c r="L60"/>
+      <c r="M60"/>
+    </row>
+    <row r="61">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+    </row>
+    <row r="62">
+      <c r="A62"/>
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
+      <c r="M62"/>
+    </row>
+    <row r="63">
+      <c r="A63"/>
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63"/>
+      <c r="I63"/>
+      <c r="J63"/>
+      <c r="K63"/>
+      <c r="L63"/>
+      <c r="M63"/>
+    </row>
+    <row r="64">
+      <c r="A64"/>
+      <c r="B64"/>
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
+      <c r="L64"/>
+      <c r="M64"/>
+    </row>
+    <row r="65">
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65"/>
+    </row>
+    <row r="66">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+      <c r="K66"/>
+      <c r="L66"/>
+      <c r="M66"/>
+    </row>
+    <row r="67">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
+    </row>
+    <row r="68">
+      <c r="A68"/>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68"/>
+      <c r="M68"/>
+    </row>
+    <row r="69">
+      <c r="A69"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69"/>
+      <c r="M69"/>
+    </row>
+    <row r="70">
+      <c r="A70"/>
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
+      <c r="I70"/>
+      <c r="J70"/>
+      <c r="K70"/>
+      <c r="L70"/>
+      <c r="M70"/>
+    </row>
+    <row r="71">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+    </row>
+    <row r="72">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72"/>
+    </row>
+    <row r="73">
+      <c r="A73"/>
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73"/>
+      <c r="G73"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="M73"/>
+    </row>
+    <row r="74">
+      <c r="A74"/>
+      <c r="B74"/>
+      <c r="C74"/>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74"/>
+      <c r="G74"/>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74"/>
+      <c r="K74"/>
+      <c r="L74"/>
+      <c r="M74"/>
+    </row>
+    <row r="75">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75"/>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="M75"/>
+    </row>
+    <row r="76">
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76"/>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
+      <c r="G76"/>
+      <c r="H76"/>
+      <c r="I76"/>
+      <c r="J76"/>
+      <c r="K76"/>
+      <c r="L76"/>
+      <c r="M76"/>
+    </row>
+    <row r="77">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
+    </row>
+    <row r="78">
+      <c r="A78"/>
+      <c r="B78"/>
+      <c r="C78"/>
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78"/>
+      <c r="I78"/>
+      <c r="J78"/>
+      <c r="K78"/>
+      <c r="L78"/>
+      <c r="M78"/>
+    </row>
+    <row r="79">
+      <c r="A79"/>
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79"/>
+      <c r="G79"/>
+      <c r="H79"/>
+      <c r="I79"/>
+      <c r="J79"/>
+      <c r="K79"/>
+      <c r="L79"/>
+      <c r="M79"/>
+    </row>
+    <row r="80">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80"/>
+      <c r="G80"/>
+      <c r="H80"/>
+      <c r="I80"/>
+      <c r="J80"/>
+      <c r="K80"/>
+      <c r="L80"/>
+      <c r="M80"/>
+    </row>
+    <row r="81">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
+      <c r="I81"/>
+      <c r="J81"/>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81"/>
+    </row>
+    <row r="82">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
+      <c r="L82"/>
+      <c r="M82"/>
+    </row>
+    <row r="83">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+      <c r="I83"/>
+      <c r="J83"/>
+      <c r="K83"/>
+      <c r="L83"/>
+      <c r="M83"/>
+    </row>
+    <row r="84">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
+      <c r="I84"/>
+      <c r="J84"/>
+      <c r="K84"/>
+      <c r="L84"/>
+      <c r="M84"/>
+    </row>
+    <row r="85">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85"/>
+      <c r="I85"/>
+      <c r="J85"/>
+      <c r="K85"/>
+      <c r="L85"/>
+      <c r="M85"/>
+    </row>
+    <row r="86">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+      <c r="I86"/>
+      <c r="J86"/>
+      <c r="K86"/>
+      <c r="L86"/>
+      <c r="M86"/>
+    </row>
+    <row r="87">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
+      <c r="K87"/>
+      <c r="L87"/>
+      <c r="M87"/>
+    </row>
+    <row r="88">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88"/>
+      <c r="J88"/>
+      <c r="K88"/>
+      <c r="L88"/>
+      <c r="M88"/>
+    </row>
+    <row r="89">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="H89"/>
+      <c r="I89"/>
+      <c r="J89"/>
+      <c r="K89"/>
+      <c r="L89"/>
+      <c r="M89"/>
+    </row>
+    <row r="90">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="H90"/>
+      <c r="I90"/>
+      <c r="J90"/>
+      <c r="K90"/>
+      <c r="L90"/>
+      <c r="M90"/>
+    </row>
+    <row r="91">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
+      <c r="L91"/>
+      <c r="M91"/>
+    </row>
+    <row r="92">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="H92"/>
+      <c r="I92"/>
+      <c r="J92"/>
+      <c r="K92"/>
+      <c r="L92"/>
+      <c r="M92"/>
+    </row>
+    <row r="93">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93"/>
+      <c r="D93"/>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="G93"/>
+      <c r="H93"/>
+      <c r="I93"/>
+      <c r="J93"/>
+      <c r="K93"/>
+      <c r="L93"/>
+      <c r="M93"/>
+    </row>
+    <row r="94">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94"/>
+      <c r="I94"/>
+      <c r="J94"/>
+      <c r="K94"/>
+      <c r="L94"/>
+      <c r="M94"/>
+    </row>
+    <row r="95">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95"/>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95"/>
+      <c r="G95"/>
+      <c r="H95"/>
+      <c r="I95"/>
+      <c r="J95"/>
+      <c r="K95"/>
+      <c r="L95"/>
+      <c r="M95"/>
+    </row>
+    <row r="96">
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96"/>
+      <c r="G96"/>
+      <c r="H96"/>
+      <c r="I96"/>
+      <c r="J96"/>
+      <c r="K96"/>
+      <c r="L96"/>
+      <c r="M96"/>
+    </row>
+    <row r="97">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+      <c r="H97"/>
+      <c r="I97"/>
+      <c r="J97"/>
+      <c r="K97"/>
+      <c r="L97"/>
+      <c r="M97"/>
+    </row>
+    <row r="98">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98"/>
+      <c r="G98"/>
+      <c r="H98"/>
+      <c r="I98"/>
+      <c r="J98"/>
+      <c r="K98"/>
+      <c r="L98"/>
+      <c r="M98"/>
+    </row>
+    <row r="99">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+      <c r="I99"/>
+      <c r="J99"/>
+      <c r="K99"/>
+      <c r="L99"/>
+      <c r="M99"/>
+    </row>
+    <row r="100">
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="H100"/>
+      <c r="I100"/>
+      <c r="J100"/>
+      <c r="K100"/>
+      <c r="L100"/>
+      <c r="M100"/>
+    </row>
+    <row r="101">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101"/>
+      <c r="M101"/>
+    </row>
+    <row r="102">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
+      <c r="L102"/>
+      <c r="M102"/>
+    </row>
+    <row r="103">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+      <c r="J103"/>
+      <c r="K103"/>
+      <c r="L103"/>
+      <c r="M103"/>
+    </row>
+    <row r="104">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+      <c r="J104"/>
+      <c r="K104"/>
+      <c r="L104"/>
+      <c r="M104"/>
+    </row>
+    <row r="105">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105"/>
+      <c r="J105"/>
+      <c r="K105"/>
+      <c r="L105"/>
+      <c r="M105"/>
+    </row>
+    <row r="106">
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106"/>
+      <c r="J106"/>
+      <c r="K106"/>
+      <c r="L106"/>
+      <c r="M106"/>
+    </row>
+    <row r="107">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+      <c r="J107"/>
+      <c r="K107"/>
+      <c r="L107"/>
+      <c r="M107"/>
+    </row>
+    <row r="108">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108"/>
+      <c r="K108"/>
+      <c r="L108"/>
+      <c r="M108"/>
+    </row>
+    <row r="109">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109"/>
+      <c r="J109"/>
+      <c r="K109"/>
+      <c r="L109"/>
+      <c r="M109"/>
+    </row>
+    <row r="110">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="K110"/>
+      <c r="L110"/>
+      <c r="M110"/>
+    </row>
+    <row r="111">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
+      <c r="L111"/>
+      <c r="M111"/>
+    </row>
+    <row r="112">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="H112"/>
+      <c r="I112"/>
+      <c r="J112"/>
+      <c r="K112"/>
+      <c r="L112"/>
+      <c r="M112"/>
+    </row>
+    <row r="113">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
+      <c r="K113"/>
+      <c r="L113"/>
+      <c r="M113"/>
+    </row>
+    <row r="114">
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="H114"/>
+      <c r="I114"/>
+      <c r="J114"/>
+      <c r="K114"/>
+      <c r="L114"/>
+      <c r="M114"/>
+    </row>
+    <row r="115">
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="H115"/>
+      <c r="I115"/>
+      <c r="J115"/>
+      <c r="K115"/>
+      <c r="L115"/>
+      <c r="M115"/>
+    </row>
+    <row r="116">
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116"/>
+      <c r="H116"/>
+      <c r="I116"/>
+      <c r="J116"/>
+      <c r="K116"/>
+      <c r="L116"/>
+      <c r="M116"/>
+    </row>
+    <row r="117">
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="H117"/>
+      <c r="I117"/>
+      <c r="J117"/>
+      <c r="K117"/>
+      <c r="L117"/>
+      <c r="M117"/>
+    </row>
+    <row r="118">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
+      <c r="H118"/>
+      <c r="I118"/>
+      <c r="J118"/>
+      <c r="K118"/>
+      <c r="L118"/>
+      <c r="M118"/>
+    </row>
+    <row r="119">
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="H119"/>
+      <c r="I119"/>
+      <c r="J119"/>
+      <c r="K119"/>
+      <c r="L119"/>
+      <c r="M119"/>
+    </row>
+    <row r="120">
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="H120"/>
+      <c r="I120"/>
+      <c r="J120"/>
+      <c r="K120"/>
+      <c r="L120"/>
+      <c r="M120"/>
+    </row>
+    <row r="121">
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
+      <c r="H121"/>
+      <c r="I121"/>
+      <c r="J121"/>
+      <c r="K121"/>
+      <c r="L121"/>
+      <c r="M121"/>
+    </row>
+    <row r="122">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="I122"/>
+      <c r="J122"/>
+      <c r="K122"/>
+      <c r="L122"/>
+      <c r="M122"/>
+    </row>
+    <row r="123">
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123"/>
+      <c r="H123"/>
+      <c r="I123"/>
+      <c r="J123"/>
+      <c r="K123"/>
+      <c r="L123"/>
+      <c r="M123"/>
+    </row>
+    <row r="124">
+      <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124"/>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
+      <c r="G124"/>
+      <c r="H124"/>
+      <c r="I124"/>
+      <c r="J124"/>
+      <c r="K124"/>
+      <c r="L124"/>
+      <c r="M124"/>
+    </row>
+    <row r="125">
+      <c r="A125"/>
+      <c r="B125"/>
+      <c r="C125"/>
+      <c r="D125"/>
+      <c r="E125"/>
+      <c r="F125"/>
+      <c r="G125"/>
+      <c r="H125"/>
+      <c r="I125"/>
+      <c r="J125"/>
+      <c r="K125"/>
+      <c r="L125"/>
+      <c r="M125"/>
+    </row>
+    <row r="126">
+      <c r="A126"/>
+      <c r="B126"/>
+      <c r="C126"/>
+      <c r="D126"/>
+      <c r="E126"/>
+      <c r="F126"/>
+      <c r="G126"/>
+      <c r="H126"/>
+      <c r="I126"/>
+      <c r="J126"/>
+      <c r="K126"/>
+      <c r="L126"/>
+      <c r="M126"/>
+    </row>
+    <row r="127">
+      <c r="A127"/>
+      <c r="B127"/>
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127"/>
+      <c r="F127"/>
+      <c r="G127"/>
+      <c r="H127"/>
+      <c r="I127"/>
+      <c r="J127"/>
+      <c r="K127"/>
+      <c r="L127"/>
+      <c r="M127"/>
+    </row>
+    <row r="128">
+      <c r="A128"/>
+      <c r="B128"/>
+      <c r="C128"/>
+      <c r="D128"/>
+      <c r="E128"/>
+      <c r="F128"/>
+      <c r="G128"/>
+      <c r="H128"/>
+      <c r="I128"/>
+      <c r="J128"/>
+      <c r="K128"/>
+      <c r="L128"/>
+      <c r="M128"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -1583,7 +1583,7 @@
     <row r="4" spans="2:9">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1597,12 +1597,14 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4"/>
+        <v>29</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4"/>
@@ -1616,12 +1618,14 @@
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5"/>
+        <v>128</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
       <c r="K5"/>
       <c r="L5"/>
       <c r="M5"/>
@@ -1634,12 +1638,8 @@
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6"/>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
+      <c r="H6"/>
+      <c r="I6"/>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
@@ -1647,43 +1647,49 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7"/>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>127</v>
+      </c>
       <c r="F7"/>
       <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7" s="8"/>
-      <c r="J7"/>
+      <c r="H7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
       <c r="K7"/>
       <c r="L7"/>
       <c r="M7"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8"/>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>127</v>
-      </c>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8" s="1" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8"/>
       <c r="L8"/>
@@ -1698,13 +1704,13 @@
       <c r="F9"/>
       <c r="G9"/>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9"/>
       <c r="L9"/>
@@ -1718,36 +1724,36 @@
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10" s="8"/>
-      <c r="J10"/>
+      <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
       <c r="K10"/>
       <c r="L10"/>
       <c r="M10"/>
     </row>
     <row r="11" spans="2:9">
       <c r="A11"/>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>127</v>
-      </c>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
       <c r="H11" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11"/>
+        <v>75</v>
+      </c>
+      <c r="J11">
+        <v>5</v>
+      </c>
       <c r="K11"/>
       <c r="L11"/>
       <c r="M11"/>
@@ -1761,12 +1767,14 @@
       <c r="F12"/>
       <c r="G12"/>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12"/>
+        <v>77</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
       <c r="K12"/>
       <c r="L12"/>
       <c r="M12"/>
@@ -1779,37 +1787,35 @@
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13" s="8"/>
-      <c r="J13"/>
+      <c r="H13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13">
+        <v>8</v>
+      </c>
       <c r="K13"/>
       <c r="L13"/>
       <c r="M13"/>
     </row>
     <row r="14" spans="2:9">
       <c r="A14"/>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>127</v>
-      </c>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K14"/>
       <c r="L14"/>
@@ -1824,13 +1830,13 @@
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K15"/>
       <c r="L15"/>
@@ -1845,13 +1851,13 @@
       <c r="F16"/>
       <c r="G16"/>
       <c r="H16" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K16"/>
       <c r="L16"/>
@@ -1866,13 +1872,13 @@
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K17"/>
       <c r="L17"/>
@@ -1887,13 +1893,13 @@
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18" s="1" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="J18" s="1">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K18"/>
       <c r="L18"/>
@@ -1908,13 +1914,13 @@
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19" s="1" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="J19" s="1">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K19"/>
       <c r="L19"/>
@@ -1929,13 +1935,13 @@
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20" s="1" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="J20" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K20"/>
       <c r="L20"/>
@@ -1950,13 +1956,13 @@
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21" s="1" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J21" s="1">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K21"/>
       <c r="L21"/>
@@ -1971,13 +1977,13 @@
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22" s="1" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J22">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K22"/>
       <c r="L22"/>
@@ -1992,13 +1998,13 @@
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23" s="1" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="J23">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K23"/>
       <c r="L23"/>
@@ -2012,35 +2018,37 @@
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
-      <c r="H24" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J24">
-        <v>17</v>
-      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24"/>
       <c r="K24"/>
       <c r="L24"/>
       <c r="M24"/>
     </row>
     <row r="25" spans="8:9">
       <c r="A25"/>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
+      <c r="B25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>127</v>
+      </c>
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" s="1" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="J25">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K25"/>
       <c r="L25"/>
@@ -2055,13 +2063,13 @@
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26" s="1" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="J26">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K26"/>
       <c r="L26"/>
@@ -2076,13 +2084,13 @@
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="J27">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K27"/>
       <c r="L27"/>
@@ -2097,13 +2105,13 @@
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="J28">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K28"/>
       <c r="L28"/>
@@ -2118,13 +2126,13 @@
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29" s="1" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="J29">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K29"/>
       <c r="L29"/>
@@ -2138,15 +2146,9 @@
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30"/>
-      <c r="H30" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="J30">
-        <v>23</v>
-      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="9"/>
+      <c r="J30"/>
       <c r="K30"/>
       <c r="L30"/>
       <c r="M30"/>
@@ -2168,29 +2170,15 @@
     </row>
     <row r="32" spans="8:9">
       <c r="A32"/>
-      <c r="B32" t="s">
-        <v>140</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>127</v>
-      </c>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
       <c r="F32"/>
       <c r="G32"/>
-      <c r="H32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="9"/>
+      <c r="J32"/>
       <c r="K32"/>
       <c r="L32"/>
       <c r="M32"/>
@@ -2203,15 +2191,9 @@
       <c r="E33"/>
       <c r="F33"/>
       <c r="G33"/>
-      <c r="H33" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="9"/>
+      <c r="J33"/>
       <c r="K33"/>
       <c r="L33"/>
       <c r="M33"/>
@@ -2224,15 +2206,9 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34"/>
-      <c r="H34" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J34">
-        <v>2</v>
-      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="9"/>
+      <c r="J34"/>
       <c r="K34"/>
       <c r="L34"/>
       <c r="M34"/>
@@ -2245,15 +2221,9 @@
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35"/>
-      <c r="H35" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J35">
-        <v>3</v>
-      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="9"/>
+      <c r="J35"/>
       <c r="K35"/>
       <c r="L35"/>
       <c r="M35"/>
@@ -2266,15 +2236,9 @@
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36"/>
-      <c r="H36" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J36">
-        <v>4</v>
-      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="9"/>
+      <c r="J36"/>
       <c r="K36"/>
       <c r="L36"/>
       <c r="M36"/>

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -86,382 +86,178 @@
     <t>注释</t>
   </si>
   <si>
-    <t>dso.Quality</t>
-  </si>
-  <si>
-    <t>COMMON</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>RARE</t>
-  </si>
-  <si>
-    <t>精良</t>
-  </si>
-  <si>
-    <t>EPIC</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>dso.BallType</t>
   </si>
   <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>Water</t>
   </si>
   <si>
     <t>纯水</t>
   </si>
   <si>
-    <t>WaterHot</t>
-  </si>
-  <si>
-    <t>热水</t>
-  </si>
-  <si>
-    <t>WaterCold</t>
-  </si>
-  <si>
-    <t>冷水</t>
-  </si>
-  <si>
     <t>Earth</t>
   </si>
   <si>
-    <t>干土</t>
-  </si>
-  <si>
-    <t>EarthWet</t>
-  </si>
-  <si>
-    <t>湿土</t>
-  </si>
-  <si>
-    <t>Sand</t>
-  </si>
-  <si>
-    <t>沙</t>
-  </si>
-  <si>
-    <t>Clay</t>
-  </si>
-  <si>
-    <t>粘土</t>
-  </si>
-  <si>
-    <t>SeedIce</t>
+    <t>纯土</t>
+  </si>
+  <si>
+    <t>dso.TileStateType</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>无状态</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>空地</t>
+  </si>
+  <si>
+    <t>Mud</t>
+  </si>
+  <si>
+    <t>普通泥浆</t>
+  </si>
+  <si>
+    <t>MudSkid</t>
+  </si>
+  <si>
+    <t>稀泥</t>
+  </si>
+  <si>
+    <t>Freeze</t>
+  </si>
+  <si>
+    <t>结冰</t>
+  </si>
+  <si>
+    <t>TerracottaBrick</t>
+  </si>
+  <si>
+    <t>陶砖</t>
+  </si>
+  <si>
+    <t>Steam</t>
+  </si>
+  <si>
+    <t>蒸汽</t>
+  </si>
+  <si>
+    <t>BasicWater</t>
+  </si>
+  <si>
+    <t>基础水</t>
+  </si>
+  <si>
+    <t>BasicEarth</t>
+  </si>
+  <si>
+    <t>基础土</t>
+  </si>
+  <si>
+    <t>BasicFire</t>
+  </si>
+  <si>
+    <t>基础火池</t>
+  </si>
+  <si>
+    <t>BasicIce</t>
+  </si>
+  <si>
+    <t>基础冰面</t>
+  </si>
+  <si>
+    <t>BasicElectricity</t>
+  </si>
+  <si>
+    <t>基础电源</t>
+  </si>
+  <si>
+    <t>BasicPlant</t>
+  </si>
+  <si>
+    <t>基础植物区</t>
+  </si>
+  <si>
+    <t>ConductZone</t>
+  </si>
+  <si>
+    <t>导电区</t>
+  </si>
+  <si>
+    <t>FlameField</t>
+  </si>
+  <si>
+    <t>燎原火海</t>
+  </si>
+  <si>
+    <t>ChargedThorn</t>
+  </si>
+  <si>
+    <t>带电荆棘</t>
+  </si>
+  <si>
+    <t>FrostSpike</t>
+  </si>
+  <si>
+    <t>霜冻冰刺</t>
+  </si>
+  <si>
+    <t>dso.SeedType</t>
+  </si>
+  <si>
+    <t>空种子</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>火种子</t>
+  </si>
+  <si>
+    <t>Elec</t>
+  </si>
+  <si>
+    <t>电种子</t>
+  </si>
+  <si>
+    <t>Ice</t>
   </si>
   <si>
     <t>冰种子</t>
   </si>
   <si>
-    <t>SeedFire</t>
-  </si>
-  <si>
-    <t>火种子</t>
-  </si>
-  <si>
-    <t>SeedPlant</t>
+    <t>Plant</t>
   </si>
   <si>
     <t>植物种子</t>
   </si>
   <si>
-    <t>SeedElec</t>
-  </si>
-  <si>
-    <t>电种子</t>
-  </si>
-  <si>
-    <t>dso.ElementTag</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>Soil</t>
-  </si>
-  <si>
-    <t>含土</t>
-  </si>
-  <si>
-    <t>含沙</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>含植物</t>
-  </si>
-  <si>
-    <t>dso.ElementType</t>
-  </si>
-  <si>
-    <t>水</t>
-  </si>
-  <si>
-    <t>土</t>
-  </si>
-  <si>
-    <t>Seed</t>
-  </si>
-  <si>
-    <t>地形种子</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>地形</t>
-  </si>
-  <si>
-    <t>dso.TileStateType</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>空地</t>
-  </si>
-  <si>
-    <t>Mud</t>
-  </si>
-  <si>
-    <t>普通泥浆</t>
-  </si>
-  <si>
-    <t>MudSkid</t>
-  </si>
-  <si>
-    <t>稀泥</t>
-  </si>
-  <si>
-    <t>Smoothie</t>
-  </si>
-  <si>
-    <t>冰沙</t>
-  </si>
-  <si>
-    <t>Freeze</t>
-  </si>
-  <si>
-    <t>结冰</t>
-  </si>
-  <si>
-    <t>TerracottaBrick</t>
-  </si>
-  <si>
-    <t>陶砖</t>
-  </si>
-  <si>
-    <t>FrozenEarth</t>
-  </si>
-  <si>
-    <t>冻土</t>
-  </si>
-  <si>
-    <t>Steam</t>
-  </si>
-  <si>
-    <t>蒸汽</t>
-  </si>
-  <si>
-    <t>ConductElectricity</t>
-  </si>
-  <si>
-    <t>导电</t>
-  </si>
-  <si>
-    <t>Vine</t>
-  </si>
-  <si>
-    <t>藤蔓</t>
-  </si>
-  <si>
-    <t>Glass</t>
-  </si>
-  <si>
-    <t>玻璃</t>
-  </si>
-  <si>
-    <t>Burn</t>
-  </si>
-  <si>
-    <t>燃烧</t>
-  </si>
-  <si>
-    <t>Ashes</t>
-  </si>
-  <si>
-    <t>灰烬</t>
-  </si>
-  <si>
-    <t>BasicWater</t>
-  </si>
-  <si>
-    <t>基础水地块</t>
-  </si>
-  <si>
-    <t>BasicEarth</t>
-  </si>
-  <si>
-    <t>基础土地块</t>
-  </si>
-  <si>
-    <t>BasicFire</t>
-  </si>
-  <si>
-    <t>基础火池</t>
-  </si>
-  <si>
-    <t>BasicIce</t>
-  </si>
-  <si>
-    <t>基础冰面</t>
-  </si>
-  <si>
-    <t>BasicElectricity</t>
-  </si>
-  <si>
-    <t>基础电源</t>
-  </si>
-  <si>
-    <t>BasicPlant</t>
-  </si>
-  <si>
-    <t>基础植物区</t>
-  </si>
-  <si>
-    <t>dso.TileEffectType</t>
-  </si>
-  <si>
-    <t>Slow</t>
-  </si>
-  <si>
-    <t>减速</t>
-  </si>
-  <si>
-    <t>Skid</t>
-  </si>
-  <si>
-    <t>打滑</t>
-  </si>
-  <si>
-    <t>Slid</t>
-  </si>
-  <si>
-    <t>滑行</t>
-  </si>
-  <si>
-    <t>KnockBack</t>
-  </si>
-  <si>
-    <t>击退</t>
-  </si>
-  <si>
-    <t>Block</t>
-  </si>
-  <si>
-    <t>阻挡</t>
-  </si>
-  <si>
-    <t>Numbness</t>
-  </si>
-  <si>
-    <t>麻痹</t>
-  </si>
-  <si>
-    <t>Fixed</t>
-  </si>
-  <si>
-    <t>定身</t>
-  </si>
-  <si>
-    <t>DamageInstant</t>
-  </si>
-  <si>
-    <t>瞬时伤害</t>
-  </si>
-  <si>
-    <t>DamageOverTime</t>
-  </si>
-  <si>
-    <t>持续伤害</t>
-  </si>
-  <si>
-    <t>InheritedTW</t>
-  </si>
-  <si>
-    <t>温湿度继承</t>
-  </si>
-  <si>
-    <t>ClearPlant</t>
-  </si>
-  <si>
-    <t>清除植物</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>纯土</t>
-  </si>
-  <si>
-    <t>无状态</t>
-  </si>
-  <si>
-    <t>基础水</t>
-  </si>
-  <si>
-    <t>基础土</t>
-  </si>
-  <si>
-    <t>ConductZone</t>
-  </si>
-  <si>
-    <t>导电区</t>
-  </si>
-  <si>
-    <t>FlameField</t>
-  </si>
-  <si>
-    <t>燎原火海</t>
-  </si>
-  <si>
-    <t>ChargedThorn</t>
-  </si>
-  <si>
-    <t>带电荆棘</t>
-  </si>
-  <si>
-    <t>FrostSpike</t>
-  </si>
-  <si>
-    <t>霜冻冰刺</t>
-  </si>
-  <si>
-    <t>dso.SeedType</t>
-  </si>
-  <si>
-    <t>空种子</t>
-  </si>
-  <si>
-    <t>Fire</t>
-  </si>
-  <si>
-    <t>Elec</t>
-  </si>
-  <si>
-    <t>Ice</t>
+    <t>dso.AudioId</t>
+  </si>
+  <si>
+    <t>BgmNormal</t>
+  </si>
+  <si>
+    <t>默认的bgm</t>
+  </si>
+  <si>
+    <t>PlayerHurt</t>
+  </si>
+  <si>
+    <t>玩家受击</t>
+  </si>
+  <si>
+    <t>PlayerDie</t>
+  </si>
+  <si>
+    <t>玩家死亡</t>
   </si>
 </sst>
 </file>
@@ -1478,9 +1274,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
@@ -1580,10 +1376,9 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:9">
-      <c r="A4"/>
+    <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1592,25 +1387,22 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-    </row>
-    <row r="5" spans="8:9">
-      <c r="A5"/>
+    </row>
+    <row r="5" spans="2:11">
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
@@ -1618,20 +1410,17 @@
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I5" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
-    </row>
-    <row r="6" spans="8:9">
-      <c r="A6"/>
+    </row>
+    <row r="6" spans="2:11">
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
@@ -1642,13 +1431,10 @@
       <c r="I6"/>
       <c r="J6"/>
       <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7"/>
+    </row>
+    <row r="7" spans="2:11">
       <c r="B7" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1657,25 +1443,22 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="F7"/>
       <c r="G7"/>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8"/>
+    </row>
+    <row r="8" spans="2:11">
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1683,20 +1466,17 @@
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8" s="1" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="A9"/>
+    </row>
+    <row r="9" spans="2:11">
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
@@ -1704,20 +1484,17 @@
       <c r="F9"/>
       <c r="G9"/>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="J9">
         <v>2</v>
       </c>
       <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="A10"/>
+    </row>
+    <row r="10" spans="2:11">
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
@@ -1725,20 +1502,17 @@
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J10">
         <v>3</v>
       </c>
       <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="A11"/>
+    </row>
+    <row r="11" spans="2:11">
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
@@ -1746,20 +1520,17 @@
       <c r="F11"/>
       <c r="G11"/>
       <c r="H11" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="J11">
         <v>5</v>
       </c>
       <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="A12"/>
+    </row>
+    <row r="12" spans="2:11">
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
@@ -1767,20 +1538,17 @@
       <c r="F12"/>
       <c r="G12"/>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="J12">
         <v>6</v>
       </c>
       <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="A13"/>
+    </row>
+    <row r="13" spans="2:11">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
@@ -1788,20 +1556,17 @@
       <c r="F13"/>
       <c r="G13"/>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="J13">
         <v>8</v>
       </c>
       <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="A14"/>
+    </row>
+    <row r="14" spans="2:11">
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1809,20 +1574,17 @@
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="J14">
         <v>14</v>
       </c>
       <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="A15"/>
+    </row>
+    <row r="15" spans="2:11">
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -1830,20 +1592,17 @@
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="J15">
         <v>15</v>
       </c>
       <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="A16"/>
+    </row>
+    <row r="16" spans="2:11">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1851,20 +1610,17 @@
       <c r="F16"/>
       <c r="G16"/>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="J16">
         <v>16</v>
       </c>
       <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="A17"/>
+    </row>
+    <row r="17" spans="2:11">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -1872,41 +1628,32 @@
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="J17">
         <v>17</v>
       </c>
       <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="A18"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+    </row>
+    <row r="18" spans="5:11">
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18" s="1" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="J18" s="1">
         <v>18</v>
       </c>
       <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18"/>
-    </row>
-    <row r="19" spans="8:10">
-      <c r="A19"/>
+    </row>
+    <row r="19" spans="2:11">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1914,20 +1661,17 @@
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19" s="1" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="J19" s="1">
         <v>19</v>
       </c>
       <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
-    </row>
-    <row r="20" spans="8:10">
-      <c r="A20"/>
+    </row>
+    <row r="20" spans="2:11">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -1935,20 +1679,17 @@
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20" s="1" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="J20" s="1">
         <v>20</v>
       </c>
       <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-    </row>
-    <row r="21" spans="8:10">
-      <c r="A21"/>
+    </row>
+    <row r="21" spans="2:11">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1956,41 +1697,32 @@
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21" s="1" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="J21" s="1">
         <v>21</v>
       </c>
       <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="A22"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+    </row>
+    <row r="22" spans="5:11">
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22" s="1" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="J22">
         <v>22</v>
       </c>
       <c r="K22"/>
-      <c r="L22"/>
-      <c r="M22"/>
-    </row>
-    <row r="23" spans="8:9">
-      <c r="A23"/>
+    </row>
+    <row r="23" spans="2:11">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -1998,37 +1730,29 @@
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23" s="1" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="J23">
         <v>23</v>
       </c>
       <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
-    </row>
-    <row r="24" spans="8:9">
-      <c r="A24"/>
+    </row>
+    <row r="24" spans="2:11">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
       <c r="J24"/>
       <c r="K24"/>
-      <c r="L24"/>
-      <c r="M24"/>
-    </row>
-    <row r="25" spans="8:9">
-      <c r="A25"/>
+    </row>
+    <row r="25" spans="2:11">
       <c r="B25" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2037,46 +1761,37 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25"/>
-      <c r="L25"/>
-      <c r="M25"/>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="A26"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+    </row>
+    <row r="26" spans="5:11">
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26" s="1" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-    </row>
-    <row r="27" spans="8:9">
-      <c r="A27"/>
+    </row>
+    <row r="27" spans="2:11">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -2084,20 +1799,17 @@
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27" s="1" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="J27">
         <v>2</v>
       </c>
       <c r="K27"/>
-      <c r="L27"/>
-      <c r="M27"/>
-    </row>
-    <row r="28" spans="8:9">
-      <c r="A28"/>
+    </row>
+    <row r="28" spans="2:11">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -2105,20 +1817,17 @@
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28" s="1" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="J28">
         <v>3</v>
       </c>
       <c r="K28"/>
-      <c r="L28"/>
-      <c r="M28"/>
-    </row>
-    <row r="29" spans="8:9">
-      <c r="A29"/>
+    </row>
+    <row r="29" spans="2:11">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -2126,440 +1835,351 @@
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="J29">
         <v>4</v>
       </c>
       <c r="K29"/>
-      <c r="L29"/>
-      <c r="M29"/>
-    </row>
-    <row r="30" spans="8:9">
-      <c r="A30"/>
+    </row>
+    <row r="30" spans="2:11">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30"/>
-      <c r="H30" s="1"/>
       <c r="I30" s="9"/>
       <c r="J30"/>
       <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30"/>
-    </row>
-    <row r="31" spans="8:9">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
+    </row>
+    <row r="31" customFormat="1" spans="2:10">
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>20</v>
+      </c>
       <c r="F31"/>
       <c r="G31"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="9"/>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
-      <c r="M31"/>
-    </row>
-    <row r="32" spans="8:9">
-      <c r="A32"/>
+      <c r="H31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
       <c r="F32"/>
       <c r="G32"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="9"/>
-      <c r="J32"/>
+      <c r="H32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
       <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-    </row>
-    <row r="33" spans="8:9">
-      <c r="A33"/>
+    </row>
+    <row r="33" spans="2:11">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
       <c r="F33"/>
       <c r="G33"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="9"/>
-      <c r="J33"/>
+      <c r="H33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J33">
+        <v>2</v>
+      </c>
       <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-    </row>
-    <row r="34" spans="8:9">
-      <c r="A34"/>
+    </row>
+    <row r="34" spans="2:11">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34"/>
-      <c r="H34" s="1"/>
       <c r="I34" s="9"/>
       <c r="J34"/>
       <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-    </row>
-    <row r="35" spans="8:9">
-      <c r="A35"/>
+    </row>
+    <row r="35" spans="2:11">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35"/>
-      <c r="H35" s="1"/>
       <c r="I35" s="9"/>
       <c r="J35"/>
       <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-    </row>
-    <row r="36" spans="8:9">
-      <c r="A36"/>
+    </row>
+    <row r="36" spans="2:11">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36"/>
-      <c r="H36" s="1"/>
       <c r="I36" s="9"/>
       <c r="J36"/>
       <c r="K36"/>
-      <c r="L36"/>
-      <c r="M36"/>
-    </row>
-    <row r="37" spans="8:9">
-      <c r="A37"/>
+    </row>
+    <row r="37" spans="2:11">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37"/>
-      <c r="H37" s="1"/>
       <c r="I37" s="9"/>
       <c r="J37"/>
       <c r="K37"/>
-      <c r="L37"/>
-      <c r="M37"/>
-    </row>
-    <row r="38" spans="8:9">
-      <c r="A38"/>
+    </row>
+    <row r="38" spans="2:11">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
-      <c r="H38" s="1"/>
       <c r="I38" s="9"/>
       <c r="J38"/>
       <c r="K38"/>
-      <c r="L38"/>
-      <c r="M38"/>
-    </row>
-    <row r="39" spans="8:9">
-      <c r="A39"/>
+    </row>
+    <row r="39" spans="2:11">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
       <c r="E39"/>
       <c r="F39"/>
       <c r="G39"/>
-      <c r="H39" s="1"/>
       <c r="I39" s="9"/>
       <c r="J39"/>
       <c r="K39"/>
-      <c r="L39"/>
-      <c r="M39"/>
-    </row>
-    <row r="40" spans="8:9">
-      <c r="A40"/>
+    </row>
+    <row r="40" spans="2:11">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40"/>
-      <c r="H40" s="1"/>
       <c r="I40" s="9"/>
       <c r="J40"/>
       <c r="K40"/>
-      <c r="L40"/>
-      <c r="M40"/>
-    </row>
-    <row r="41" spans="8:9">
-      <c r="A41"/>
+    </row>
+    <row r="41" spans="2:11">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41"/>
-      <c r="H41" s="1"/>
       <c r="I41" s="9"/>
       <c r="J41"/>
       <c r="K41"/>
-      <c r="L41"/>
-      <c r="M41"/>
-    </row>
-    <row r="42" spans="8:9">
-      <c r="A42"/>
+    </row>
+    <row r="42" spans="2:11">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42"/>
-      <c r="H42" s="1"/>
       <c r="I42" s="9"/>
       <c r="J42"/>
       <c r="K42"/>
-      <c r="L42"/>
-      <c r="M42"/>
-    </row>
-    <row r="43" spans="8:9">
-      <c r="A43"/>
+    </row>
+    <row r="43" spans="2:11">
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43"/>
-      <c r="H43" s="1"/>
       <c r="I43" s="9"/>
       <c r="J43"/>
       <c r="K43"/>
-      <c r="L43"/>
-      <c r="M43"/>
-    </row>
-    <row r="44" spans="8:9">
-      <c r="A44"/>
+    </row>
+    <row r="44" spans="2:11">
       <c r="B44"/>
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44"/>
-      <c r="H44" s="1"/>
       <c r="I44" s="9"/>
       <c r="J44"/>
       <c r="K44"/>
-      <c r="L44"/>
-      <c r="M44"/>
-    </row>
-    <row r="45" spans="8:9">
-      <c r="A45"/>
+    </row>
+    <row r="45" spans="2:11">
       <c r="B45"/>
       <c r="C45"/>
       <c r="D45"/>
       <c r="E45"/>
       <c r="F45"/>
       <c r="G45"/>
-      <c r="H45" s="1"/>
       <c r="I45" s="9"/>
       <c r="J45"/>
       <c r="K45"/>
-      <c r="L45"/>
-      <c r="M45"/>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="A46"/>
+    </row>
+    <row r="46" spans="2:11">
       <c r="B46" s="5"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46"/>
-      <c r="H46" s="1"/>
       <c r="I46" s="5"/>
       <c r="J46"/>
       <c r="K46"/>
-      <c r="L46"/>
-      <c r="M46"/>
-    </row>
-    <row r="47" spans="8:9">
-      <c r="A47"/>
+    </row>
+    <row r="47" spans="2:11">
       <c r="B47"/>
       <c r="C47"/>
       <c r="D47"/>
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47"/>
-      <c r="H47" s="1"/>
       <c r="I47" s="10"/>
       <c r="J47"/>
       <c r="K47"/>
-      <c r="L47"/>
-      <c r="M47"/>
-    </row>
-    <row r="48" spans="8:9">
-      <c r="A48"/>
+    </row>
+    <row r="48" spans="2:11">
       <c r="B48"/>
       <c r="C48"/>
       <c r="D48"/>
       <c r="E48"/>
       <c r="F48"/>
       <c r="G48"/>
-      <c r="H48" s="1"/>
       <c r="I48" s="10"/>
       <c r="J48"/>
       <c r="K48"/>
-      <c r="L48"/>
-      <c r="M48"/>
-    </row>
-    <row r="49" spans="8:9">
-      <c r="A49"/>
+    </row>
+    <row r="49" spans="2:11">
       <c r="B49"/>
       <c r="C49"/>
       <c r="D49"/>
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49"/>
-      <c r="H49" s="1"/>
       <c r="I49" s="10"/>
       <c r="J49"/>
       <c r="K49"/>
-      <c r="L49"/>
-      <c r="M49"/>
-    </row>
-    <row r="50" spans="8:9">
-      <c r="A50"/>
+    </row>
+    <row r="50" spans="2:11">
       <c r="B50"/>
       <c r="C50"/>
       <c r="D50"/>
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50"/>
-      <c r="H50" s="1"/>
       <c r="I50" s="10"/>
       <c r="J50"/>
       <c r="K50"/>
-      <c r="L50"/>
-      <c r="M50"/>
-    </row>
-    <row r="51" spans="8:9">
-      <c r="A51"/>
+    </row>
+    <row r="51" spans="2:11">
       <c r="B51"/>
       <c r="C51"/>
       <c r="D51"/>
       <c r="E51"/>
       <c r="F51"/>
       <c r="G51"/>
-      <c r="H51" s="1"/>
       <c r="I51" s="10"/>
       <c r="J51"/>
       <c r="K51"/>
-      <c r="L51"/>
-      <c r="M51"/>
-    </row>
-    <row r="52" spans="8:9">
-      <c r="A52"/>
+    </row>
+    <row r="52" spans="2:11">
       <c r="B52"/>
       <c r="C52"/>
       <c r="D52"/>
       <c r="E52"/>
       <c r="F52"/>
       <c r="G52"/>
-      <c r="H52" s="1"/>
       <c r="I52" s="10"/>
       <c r="J52"/>
       <c r="K52"/>
-      <c r="L52"/>
-      <c r="M52"/>
-    </row>
-    <row r="53" spans="8:9">
-      <c r="A53"/>
+    </row>
+    <row r="53" spans="2:11">
       <c r="B53"/>
       <c r="C53"/>
       <c r="D53"/>
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53"/>
-      <c r="H53" s="1"/>
       <c r="I53" s="10"/>
       <c r="J53"/>
       <c r="K53"/>
-      <c r="L53"/>
-      <c r="M53"/>
-    </row>
-    <row r="54" spans="8:9">
-      <c r="A54"/>
+    </row>
+    <row r="54" spans="2:11">
       <c r="B54"/>
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
       <c r="G54"/>
-      <c r="H54" s="1"/>
       <c r="I54" s="10"/>
       <c r="J54"/>
       <c r="K54"/>
-      <c r="L54"/>
-      <c r="M54"/>
-    </row>
-    <row r="55" spans="8:9">
-      <c r="A55"/>
+    </row>
+    <row r="55" spans="2:11">
       <c r="B55"/>
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
       <c r="G55"/>
-      <c r="H55" s="1"/>
       <c r="I55" s="10"/>
       <c r="J55"/>
       <c r="K55"/>
-      <c r="L55"/>
-      <c r="M55"/>
-    </row>
-    <row r="56" spans="8:9">
-      <c r="A56"/>
+    </row>
+    <row r="56" spans="2:11">
       <c r="B56"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
       <c r="F56"/>
       <c r="G56"/>
-      <c r="H56" s="1"/>
       <c r="I56" s="10"/>
       <c r="J56"/>
       <c r="K56"/>
-      <c r="L56"/>
-      <c r="M56"/>
-    </row>
-    <row r="57" spans="8:9">
-      <c r="A57"/>
+    </row>
+    <row r="57" spans="2:11">
       <c r="B57"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
       <c r="F57"/>
       <c r="G57"/>
-      <c r="H57" s="1"/>
       <c r="I57" s="10"/>
       <c r="J57"/>
       <c r="K57"/>
-      <c r="L57"/>
-      <c r="M57"/>
-    </row>
-    <row r="58">
-      <c r="A58"/>
+    </row>
+    <row r="58" spans="2:11">
       <c r="B58"/>
       <c r="C58"/>
       <c r="D58"/>
@@ -2570,11 +2190,8 @@
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
-      <c r="L58"/>
-      <c r="M58"/>
-    </row>
-    <row r="59">
-      <c r="A59"/>
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59"/>
       <c r="C59"/>
       <c r="D59"/>
@@ -2585,11 +2202,8 @@
       <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
-      <c r="L59"/>
-      <c r="M59"/>
-    </row>
-    <row r="60">
-      <c r="A60"/>
+    </row>
+    <row r="60" spans="2:11">
       <c r="B60"/>
       <c r="C60"/>
       <c r="D60"/>
@@ -2600,11 +2214,8 @@
       <c r="I60"/>
       <c r="J60"/>
       <c r="K60"/>
-      <c r="L60"/>
-      <c r="M60"/>
-    </row>
-    <row r="61">
-      <c r="A61"/>
+    </row>
+    <row r="61" spans="2:11">
       <c r="B61"/>
       <c r="C61"/>
       <c r="D61"/>
@@ -2615,11 +2226,8 @@
       <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
-      <c r="L61"/>
-      <c r="M61"/>
-    </row>
-    <row r="62">
-      <c r="A62"/>
+    </row>
+    <row r="62" spans="2:11">
       <c r="B62"/>
       <c r="C62"/>
       <c r="D62"/>
@@ -2630,11 +2238,8 @@
       <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
-      <c r="L62"/>
-      <c r="M62"/>
-    </row>
-    <row r="63">
-      <c r="A63"/>
+    </row>
+    <row r="63" spans="2:11">
       <c r="B63"/>
       <c r="C63"/>
       <c r="D63"/>
@@ -2645,11 +2250,8 @@
       <c r="I63"/>
       <c r="J63"/>
       <c r="K63"/>
-      <c r="L63"/>
-      <c r="M63"/>
-    </row>
-    <row r="64">
-      <c r="A64"/>
+    </row>
+    <row r="64" spans="2:11">
       <c r="B64"/>
       <c r="C64"/>
       <c r="D64"/>
@@ -2660,11 +2262,8 @@
       <c r="I64"/>
       <c r="J64"/>
       <c r="K64"/>
-      <c r="L64"/>
-      <c r="M64"/>
-    </row>
-    <row r="65">
-      <c r="A65"/>
+    </row>
+    <row r="65" spans="2:11">
       <c r="B65"/>
       <c r="C65"/>
       <c r="D65"/>
@@ -2675,11 +2274,8 @@
       <c r="I65"/>
       <c r="J65"/>
       <c r="K65"/>
-      <c r="L65"/>
-      <c r="M65"/>
-    </row>
-    <row r="66">
-      <c r="A66"/>
+    </row>
+    <row r="66" spans="2:11">
       <c r="B66"/>
       <c r="C66"/>
       <c r="D66"/>
@@ -2690,11 +2286,8 @@
       <c r="I66"/>
       <c r="J66"/>
       <c r="K66"/>
-      <c r="L66"/>
-      <c r="M66"/>
-    </row>
-    <row r="67">
-      <c r="A67"/>
+    </row>
+    <row r="67" spans="2:11">
       <c r="B67"/>
       <c r="C67"/>
       <c r="D67"/>
@@ -2705,11 +2298,8 @@
       <c r="I67"/>
       <c r="J67"/>
       <c r="K67"/>
-      <c r="L67"/>
-      <c r="M67"/>
-    </row>
-    <row r="68">
-      <c r="A68"/>
+    </row>
+    <row r="68" spans="2:11">
       <c r="B68"/>
       <c r="C68"/>
       <c r="D68"/>
@@ -2720,11 +2310,8 @@
       <c r="I68"/>
       <c r="J68"/>
       <c r="K68"/>
-      <c r="L68"/>
-      <c r="M68"/>
-    </row>
-    <row r="69">
-      <c r="A69"/>
+    </row>
+    <row r="69" spans="2:11">
       <c r="B69"/>
       <c r="C69"/>
       <c r="D69"/>
@@ -2735,11 +2322,8 @@
       <c r="I69"/>
       <c r="J69"/>
       <c r="K69"/>
-      <c r="L69"/>
-      <c r="M69"/>
-    </row>
-    <row r="70">
-      <c r="A70"/>
+    </row>
+    <row r="70" spans="2:11">
       <c r="B70"/>
       <c r="C70"/>
       <c r="D70"/>
@@ -2750,11 +2334,8 @@
       <c r="I70"/>
       <c r="J70"/>
       <c r="K70"/>
-      <c r="L70"/>
-      <c r="M70"/>
-    </row>
-    <row r="71">
-      <c r="A71"/>
+    </row>
+    <row r="71" spans="2:11">
       <c r="B71"/>
       <c r="C71"/>
       <c r="D71"/>
@@ -2765,11 +2346,8 @@
       <c r="I71"/>
       <c r="J71"/>
       <c r="K71"/>
-      <c r="L71"/>
-      <c r="M71"/>
-    </row>
-    <row r="72">
-      <c r="A72"/>
+    </row>
+    <row r="72" spans="2:11">
       <c r="B72"/>
       <c r="C72"/>
       <c r="D72"/>
@@ -2780,11 +2358,8 @@
       <c r="I72"/>
       <c r="J72"/>
       <c r="K72"/>
-      <c r="L72"/>
-      <c r="M72"/>
-    </row>
-    <row r="73">
-      <c r="A73"/>
+    </row>
+    <row r="73" spans="2:11">
       <c r="B73"/>
       <c r="C73"/>
       <c r="D73"/>
@@ -2795,11 +2370,8 @@
       <c r="I73"/>
       <c r="J73"/>
       <c r="K73"/>
-      <c r="L73"/>
-      <c r="M73"/>
-    </row>
-    <row r="74">
-      <c r="A74"/>
+    </row>
+    <row r="74" spans="2:11">
       <c r="B74"/>
       <c r="C74"/>
       <c r="D74"/>
@@ -2810,11 +2382,8 @@
       <c r="I74"/>
       <c r="J74"/>
       <c r="K74"/>
-      <c r="L74"/>
-      <c r="M74"/>
-    </row>
-    <row r="75">
-      <c r="A75"/>
+    </row>
+    <row r="75" spans="2:11">
       <c r="B75"/>
       <c r="C75"/>
       <c r="D75"/>
@@ -2825,11 +2394,8 @@
       <c r="I75"/>
       <c r="J75"/>
       <c r="K75"/>
-      <c r="L75"/>
-      <c r="M75"/>
-    </row>
-    <row r="76">
-      <c r="A76"/>
+    </row>
+    <row r="76" spans="2:11">
       <c r="B76"/>
       <c r="C76"/>
       <c r="D76"/>
@@ -2840,11 +2406,8 @@
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76"/>
-      <c r="L76"/>
-      <c r="M76"/>
-    </row>
-    <row r="77">
-      <c r="A77"/>
+    </row>
+    <row r="77" spans="2:11">
       <c r="B77"/>
       <c r="C77"/>
       <c r="D77"/>
@@ -2855,11 +2418,8 @@
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
-      <c r="L77"/>
-      <c r="M77"/>
-    </row>
-    <row r="78">
-      <c r="A78"/>
+    </row>
+    <row r="78" spans="2:11">
       <c r="B78"/>
       <c r="C78"/>
       <c r="D78"/>
@@ -2870,11 +2430,8 @@
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
-      <c r="L78"/>
-      <c r="M78"/>
-    </row>
-    <row r="79">
-      <c r="A79"/>
+    </row>
+    <row r="79" spans="2:11">
       <c r="B79"/>
       <c r="C79"/>
       <c r="D79"/>
@@ -2885,11 +2442,8 @@
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
-      <c r="L79"/>
-      <c r="M79"/>
-    </row>
-    <row r="80">
-      <c r="A80"/>
+    </row>
+    <row r="80" spans="2:11">
       <c r="B80"/>
       <c r="C80"/>
       <c r="D80"/>
@@ -2900,11 +2454,8 @@
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
-      <c r="L80"/>
-      <c r="M80"/>
-    </row>
-    <row r="81">
-      <c r="A81"/>
+    </row>
+    <row r="81" spans="2:11">
       <c r="B81"/>
       <c r="C81"/>
       <c r="D81"/>
@@ -2915,11 +2466,8 @@
       <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
-      <c r="L81"/>
-      <c r="M81"/>
-    </row>
-    <row r="82">
-      <c r="A82"/>
+    </row>
+    <row r="82" spans="2:11">
       <c r="B82"/>
       <c r="C82"/>
       <c r="D82"/>
@@ -2930,11 +2478,8 @@
       <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
-      <c r="L82"/>
-      <c r="M82"/>
-    </row>
-    <row r="83">
-      <c r="A83"/>
+    </row>
+    <row r="83" spans="2:11">
       <c r="B83"/>
       <c r="C83"/>
       <c r="D83"/>
@@ -2945,11 +2490,8 @@
       <c r="I83"/>
       <c r="J83"/>
       <c r="K83"/>
-      <c r="L83"/>
-      <c r="M83"/>
-    </row>
-    <row r="84">
-      <c r="A84"/>
+    </row>
+    <row r="84" spans="2:11">
       <c r="B84"/>
       <c r="C84"/>
       <c r="D84"/>
@@ -2960,11 +2502,8 @@
       <c r="I84"/>
       <c r="J84"/>
       <c r="K84"/>
-      <c r="L84"/>
-      <c r="M84"/>
-    </row>
-    <row r="85">
-      <c r="A85"/>
+    </row>
+    <row r="85" spans="2:11">
       <c r="B85"/>
       <c r="C85"/>
       <c r="D85"/>
@@ -2975,11 +2514,8 @@
       <c r="I85"/>
       <c r="J85"/>
       <c r="K85"/>
-      <c r="L85"/>
-      <c r="M85"/>
-    </row>
-    <row r="86">
-      <c r="A86"/>
+    </row>
+    <row r="86" spans="2:11">
       <c r="B86"/>
       <c r="C86"/>
       <c r="D86"/>
@@ -2990,11 +2526,8 @@
       <c r="I86"/>
       <c r="J86"/>
       <c r="K86"/>
-      <c r="L86"/>
-      <c r="M86"/>
-    </row>
-    <row r="87">
-      <c r="A87"/>
+    </row>
+    <row r="87" spans="2:11">
       <c r="B87"/>
       <c r="C87"/>
       <c r="D87"/>
@@ -3005,11 +2538,8 @@
       <c r="I87"/>
       <c r="J87"/>
       <c r="K87"/>
-      <c r="L87"/>
-      <c r="M87"/>
-    </row>
-    <row r="88">
-      <c r="A88"/>
+    </row>
+    <row r="88" spans="2:11">
       <c r="B88"/>
       <c r="C88"/>
       <c r="D88"/>
@@ -3020,11 +2550,8 @@
       <c r="I88"/>
       <c r="J88"/>
       <c r="K88"/>
-      <c r="L88"/>
-      <c r="M88"/>
-    </row>
-    <row r="89">
-      <c r="A89"/>
+    </row>
+    <row r="89" spans="2:11">
       <c r="B89"/>
       <c r="C89"/>
       <c r="D89"/>
@@ -3035,11 +2562,8 @@
       <c r="I89"/>
       <c r="J89"/>
       <c r="K89"/>
-      <c r="L89"/>
-      <c r="M89"/>
-    </row>
-    <row r="90">
-      <c r="A90"/>
+    </row>
+    <row r="90" spans="2:11">
       <c r="B90"/>
       <c r="C90"/>
       <c r="D90"/>
@@ -3050,11 +2574,8 @@
       <c r="I90"/>
       <c r="J90"/>
       <c r="K90"/>
-      <c r="L90"/>
-      <c r="M90"/>
-    </row>
-    <row r="91">
-      <c r="A91"/>
+    </row>
+    <row r="91" spans="2:11">
       <c r="B91"/>
       <c r="C91"/>
       <c r="D91"/>
@@ -3065,11 +2586,8 @@
       <c r="I91"/>
       <c r="J91"/>
       <c r="K91"/>
-      <c r="L91"/>
-      <c r="M91"/>
-    </row>
-    <row r="92">
-      <c r="A92"/>
+    </row>
+    <row r="92" spans="2:11">
       <c r="B92"/>
       <c r="C92"/>
       <c r="D92"/>
@@ -3080,11 +2598,8 @@
       <c r="I92"/>
       <c r="J92"/>
       <c r="K92"/>
-      <c r="L92"/>
-      <c r="M92"/>
-    </row>
-    <row r="93">
-      <c r="A93"/>
+    </row>
+    <row r="93" spans="2:11">
       <c r="B93"/>
       <c r="C93"/>
       <c r="D93"/>
@@ -3095,11 +2610,8 @@
       <c r="I93"/>
       <c r="J93"/>
       <c r="K93"/>
-      <c r="L93"/>
-      <c r="M93"/>
-    </row>
-    <row r="94">
-      <c r="A94"/>
+    </row>
+    <row r="94" spans="2:11">
       <c r="B94"/>
       <c r="C94"/>
       <c r="D94"/>
@@ -3110,11 +2622,8 @@
       <c r="I94"/>
       <c r="J94"/>
       <c r="K94"/>
-      <c r="L94"/>
-      <c r="M94"/>
-    </row>
-    <row r="95">
-      <c r="A95"/>
+    </row>
+    <row r="95" spans="2:11">
       <c r="B95"/>
       <c r="C95"/>
       <c r="D95"/>
@@ -3125,11 +2634,8 @@
       <c r="I95"/>
       <c r="J95"/>
       <c r="K95"/>
-      <c r="L95"/>
-      <c r="M95"/>
-    </row>
-    <row r="96">
-      <c r="A96"/>
+    </row>
+    <row r="96" spans="2:11">
       <c r="B96"/>
       <c r="C96"/>
       <c r="D96"/>
@@ -3140,11 +2646,8 @@
       <c r="I96"/>
       <c r="J96"/>
       <c r="K96"/>
-      <c r="L96"/>
-      <c r="M96"/>
-    </row>
-    <row r="97">
-      <c r="A97"/>
+    </row>
+    <row r="97" spans="2:11">
       <c r="B97"/>
       <c r="C97"/>
       <c r="D97"/>
@@ -3155,11 +2658,8 @@
       <c r="I97"/>
       <c r="J97"/>
       <c r="K97"/>
-      <c r="L97"/>
-      <c r="M97"/>
-    </row>
-    <row r="98">
-      <c r="A98"/>
+    </row>
+    <row r="98" spans="2:11">
       <c r="B98"/>
       <c r="C98"/>
       <c r="D98"/>
@@ -3170,11 +2670,8 @@
       <c r="I98"/>
       <c r="J98"/>
       <c r="K98"/>
-      <c r="L98"/>
-      <c r="M98"/>
-    </row>
-    <row r="99">
-      <c r="A99"/>
+    </row>
+    <row r="99" spans="2:11">
       <c r="B99"/>
       <c r="C99"/>
       <c r="D99"/>
@@ -3185,11 +2682,8 @@
       <c r="I99"/>
       <c r="J99"/>
       <c r="K99"/>
-      <c r="L99"/>
-      <c r="M99"/>
-    </row>
-    <row r="100">
-      <c r="A100"/>
+    </row>
+    <row r="100" spans="2:11">
       <c r="B100"/>
       <c r="C100"/>
       <c r="D100"/>
@@ -3200,11 +2694,8 @@
       <c r="I100"/>
       <c r="J100"/>
       <c r="K100"/>
-      <c r="L100"/>
-      <c r="M100"/>
-    </row>
-    <row r="101">
-      <c r="A101"/>
+    </row>
+    <row r="101" spans="2:11">
       <c r="B101"/>
       <c r="C101"/>
       <c r="D101"/>
@@ -3215,11 +2706,8 @@
       <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
-      <c r="L101"/>
-      <c r="M101"/>
-    </row>
-    <row r="102">
-      <c r="A102"/>
+    </row>
+    <row r="102" spans="2:11">
       <c r="B102"/>
       <c r="C102"/>
       <c r="D102"/>
@@ -3230,11 +2718,8 @@
       <c r="I102"/>
       <c r="J102"/>
       <c r="K102"/>
-      <c r="L102"/>
-      <c r="M102"/>
-    </row>
-    <row r="103">
-      <c r="A103"/>
+    </row>
+    <row r="103" spans="2:11">
       <c r="B103"/>
       <c r="C103"/>
       <c r="D103"/>
@@ -3245,11 +2730,8 @@
       <c r="I103"/>
       <c r="J103"/>
       <c r="K103"/>
-      <c r="L103"/>
-      <c r="M103"/>
-    </row>
-    <row r="104">
-      <c r="A104"/>
+    </row>
+    <row r="104" spans="2:11">
       <c r="B104"/>
       <c r="C104"/>
       <c r="D104"/>
@@ -3260,11 +2742,8 @@
       <c r="I104"/>
       <c r="J104"/>
       <c r="K104"/>
-      <c r="L104"/>
-      <c r="M104"/>
-    </row>
-    <row r="105">
-      <c r="A105"/>
+    </row>
+    <row r="105" spans="2:11">
       <c r="B105"/>
       <c r="C105"/>
       <c r="D105"/>
@@ -3275,11 +2754,8 @@
       <c r="I105"/>
       <c r="J105"/>
       <c r="K105"/>
-      <c r="L105"/>
-      <c r="M105"/>
-    </row>
-    <row r="106">
-      <c r="A106"/>
+    </row>
+    <row r="106" spans="2:11">
       <c r="B106"/>
       <c r="C106"/>
       <c r="D106"/>
@@ -3290,11 +2766,8 @@
       <c r="I106"/>
       <c r="J106"/>
       <c r="K106"/>
-      <c r="L106"/>
-      <c r="M106"/>
-    </row>
-    <row r="107">
-      <c r="A107"/>
+    </row>
+    <row r="107" spans="2:11">
       <c r="B107"/>
       <c r="C107"/>
       <c r="D107"/>
@@ -3305,11 +2778,8 @@
       <c r="I107"/>
       <c r="J107"/>
       <c r="K107"/>
-      <c r="L107"/>
-      <c r="M107"/>
-    </row>
-    <row r="108">
-      <c r="A108"/>
+    </row>
+    <row r="108" spans="2:11">
       <c r="B108"/>
       <c r="C108"/>
       <c r="D108"/>
@@ -3320,11 +2790,8 @@
       <c r="I108"/>
       <c r="J108"/>
       <c r="K108"/>
-      <c r="L108"/>
-      <c r="M108"/>
-    </row>
-    <row r="109">
-      <c r="A109"/>
+    </row>
+    <row r="109" spans="2:11">
       <c r="B109"/>
       <c r="C109"/>
       <c r="D109"/>
@@ -3335,11 +2802,8 @@
       <c r="I109"/>
       <c r="J109"/>
       <c r="K109"/>
-      <c r="L109"/>
-      <c r="M109"/>
-    </row>
-    <row r="110">
-      <c r="A110"/>
+    </row>
+    <row r="110" spans="2:11">
       <c r="B110"/>
       <c r="C110"/>
       <c r="D110"/>
@@ -3350,11 +2814,8 @@
       <c r="I110"/>
       <c r="J110"/>
       <c r="K110"/>
-      <c r="L110"/>
-      <c r="M110"/>
-    </row>
-    <row r="111">
-      <c r="A111"/>
+    </row>
+    <row r="111" spans="2:11">
       <c r="B111"/>
       <c r="C111"/>
       <c r="D111"/>
@@ -3365,11 +2826,8 @@
       <c r="I111"/>
       <c r="J111"/>
       <c r="K111"/>
-      <c r="L111"/>
-      <c r="M111"/>
-    </row>
-    <row r="112">
-      <c r="A112"/>
+    </row>
+    <row r="112" spans="2:11">
       <c r="B112"/>
       <c r="C112"/>
       <c r="D112"/>
@@ -3380,11 +2838,8 @@
       <c r="I112"/>
       <c r="J112"/>
       <c r="K112"/>
-      <c r="L112"/>
-      <c r="M112"/>
-    </row>
-    <row r="113">
-      <c r="A113"/>
+    </row>
+    <row r="113" spans="2:11">
       <c r="B113"/>
       <c r="C113"/>
       <c r="D113"/>
@@ -3395,11 +2850,8 @@
       <c r="I113"/>
       <c r="J113"/>
       <c r="K113"/>
-      <c r="L113"/>
-      <c r="M113"/>
-    </row>
-    <row r="114">
-      <c r="A114"/>
+    </row>
+    <row r="114" spans="2:11">
       <c r="B114"/>
       <c r="C114"/>
       <c r="D114"/>
@@ -3410,11 +2862,8 @@
       <c r="I114"/>
       <c r="J114"/>
       <c r="K114"/>
-      <c r="L114"/>
-      <c r="M114"/>
-    </row>
-    <row r="115">
-      <c r="A115"/>
+    </row>
+    <row r="115" spans="2:11">
       <c r="B115"/>
       <c r="C115"/>
       <c r="D115"/>
@@ -3425,11 +2874,8 @@
       <c r="I115"/>
       <c r="J115"/>
       <c r="K115"/>
-      <c r="L115"/>
-      <c r="M115"/>
-    </row>
-    <row r="116">
-      <c r="A116"/>
+    </row>
+    <row r="116" spans="2:11">
       <c r="B116"/>
       <c r="C116"/>
       <c r="D116"/>
@@ -3440,11 +2886,8 @@
       <c r="I116"/>
       <c r="J116"/>
       <c r="K116"/>
-      <c r="L116"/>
-      <c r="M116"/>
-    </row>
-    <row r="117">
-      <c r="A117"/>
+    </row>
+    <row r="117" spans="2:11">
       <c r="B117"/>
       <c r="C117"/>
       <c r="D117"/>
@@ -3455,11 +2898,8 @@
       <c r="I117"/>
       <c r="J117"/>
       <c r="K117"/>
-      <c r="L117"/>
-      <c r="M117"/>
-    </row>
-    <row r="118">
-      <c r="A118"/>
+    </row>
+    <row r="118" spans="2:11">
       <c r="B118"/>
       <c r="C118"/>
       <c r="D118"/>
@@ -3470,11 +2910,8 @@
       <c r="I118"/>
       <c r="J118"/>
       <c r="K118"/>
-      <c r="L118"/>
-      <c r="M118"/>
-    </row>
-    <row r="119">
-      <c r="A119"/>
+    </row>
+    <row r="119" spans="2:11">
       <c r="B119"/>
       <c r="C119"/>
       <c r="D119"/>
@@ -3485,11 +2922,8 @@
       <c r="I119"/>
       <c r="J119"/>
       <c r="K119"/>
-      <c r="L119"/>
-      <c r="M119"/>
-    </row>
-    <row r="120">
-      <c r="A120"/>
+    </row>
+    <row r="120" spans="2:11">
       <c r="B120"/>
       <c r="C120"/>
       <c r="D120"/>
@@ -3500,11 +2934,8 @@
       <c r="I120"/>
       <c r="J120"/>
       <c r="K120"/>
-      <c r="L120"/>
-      <c r="M120"/>
-    </row>
-    <row r="121">
-      <c r="A121"/>
+    </row>
+    <row r="121" spans="2:11">
       <c r="B121"/>
       <c r="C121"/>
       <c r="D121"/>
@@ -3515,11 +2946,8 @@
       <c r="I121"/>
       <c r="J121"/>
       <c r="K121"/>
-      <c r="L121"/>
-      <c r="M121"/>
-    </row>
-    <row r="122">
-      <c r="A122"/>
+    </row>
+    <row r="122" spans="2:11">
       <c r="B122"/>
       <c r="C122"/>
       <c r="D122"/>
@@ -3530,11 +2958,8 @@
       <c r="I122"/>
       <c r="J122"/>
       <c r="K122"/>
-      <c r="L122"/>
-      <c r="M122"/>
-    </row>
-    <row r="123">
-      <c r="A123"/>
+    </row>
+    <row r="123" spans="2:11">
       <c r="B123"/>
       <c r="C123"/>
       <c r="D123"/>
@@ -3545,11 +2970,8 @@
       <c r="I123"/>
       <c r="J123"/>
       <c r="K123"/>
-      <c r="L123"/>
-      <c r="M123"/>
-    </row>
-    <row r="124">
-      <c r="A124"/>
+    </row>
+    <row r="124" spans="2:11">
       <c r="B124"/>
       <c r="C124"/>
       <c r="D124"/>
@@ -3560,11 +2982,8 @@
       <c r="I124"/>
       <c r="J124"/>
       <c r="K124"/>
-      <c r="L124"/>
-      <c r="M124"/>
-    </row>
-    <row r="125">
-      <c r="A125"/>
+    </row>
+    <row r="125" spans="2:11">
       <c r="B125"/>
       <c r="C125"/>
       <c r="D125"/>
@@ -3575,11 +2994,8 @@
       <c r="I125"/>
       <c r="J125"/>
       <c r="K125"/>
-      <c r="L125"/>
-      <c r="M125"/>
-    </row>
-    <row r="126">
-      <c r="A126"/>
+    </row>
+    <row r="126" spans="2:11">
       <c r="B126"/>
       <c r="C126"/>
       <c r="D126"/>
@@ -3590,11 +3006,8 @@
       <c r="I126"/>
       <c r="J126"/>
       <c r="K126"/>
-      <c r="L126"/>
-      <c r="M126"/>
-    </row>
-    <row r="127">
-      <c r="A127"/>
+    </row>
+    <row r="127" spans="2:11">
       <c r="B127"/>
       <c r="C127"/>
       <c r="D127"/>
@@ -3605,11 +3018,8 @@
       <c r="I127"/>
       <c r="J127"/>
       <c r="K127"/>
-      <c r="L127"/>
-      <c r="M127"/>
-    </row>
-    <row r="128">
-      <c r="A128"/>
+    </row>
+    <row r="128" spans="2:11">
       <c r="B128"/>
       <c r="C128"/>
       <c r="D128"/>
@@ -3620,8 +3030,6 @@
       <c r="I128"/>
       <c r="J128"/>
       <c r="K128"/>
-      <c r="L128"/>
-      <c r="M128"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="25160" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="131">
   <si>
     <t>##var</t>
   </si>
@@ -248,16 +248,178 @@
     <t>默认的bgm</t>
   </si>
   <si>
-    <t>PlayerHurt</t>
-  </si>
-  <si>
-    <t>玩家受击</t>
-  </si>
-  <si>
-    <t>PlayerDie</t>
-  </si>
-  <si>
-    <t>玩家死亡</t>
+    <t>UIButtonClick</t>
+  </si>
+  <si>
+    <t>UI通用按钮点击</t>
+  </si>
+  <si>
+    <t>UIVolumeSlide</t>
+  </si>
+  <si>
+    <t>UI音量音效条滑动</t>
+  </si>
+  <si>
+    <t>WaveCountdown</t>
+  </si>
+  <si>
+    <t>波次三秒倒计时</t>
+  </si>
+  <si>
+    <t>StoryCGPopup</t>
+  </si>
+  <si>
+    <t>剧情CG弹出</t>
+  </si>
+  <si>
+    <t>PlayerThrowStart</t>
+  </si>
+  <si>
+    <t>玩家投掷开始</t>
+  </si>
+  <si>
+    <t>PlayerThrowLand</t>
+  </si>
+  <si>
+    <t>玩家投掷落地</t>
+  </si>
+  <si>
+    <t>PlayerPickup</t>
+  </si>
+  <si>
+    <t>玩家拾取</t>
+  </si>
+  <si>
+    <t>PlayerMove</t>
+  </si>
+  <si>
+    <t>玩家移动</t>
+  </si>
+  <si>
+    <t>PlayerDiscard</t>
+  </si>
+  <si>
+    <t>玩家丢弃资源</t>
+  </si>
+  <si>
+    <t>TileSteam</t>
+  </si>
+  <si>
+    <t>地块水蒸气</t>
+  </si>
+  <si>
+    <t>TileFreeze</t>
+  </si>
+  <si>
+    <t>地块结冰</t>
+  </si>
+  <si>
+    <t>TileIceShard</t>
+  </si>
+  <si>
+    <t>地块冰沙</t>
+  </si>
+  <si>
+    <t>TileBurn</t>
+  </si>
+  <si>
+    <t>地块燃烧</t>
+  </si>
+  <si>
+    <t>TileAsh</t>
+  </si>
+  <si>
+    <t>地块化为灰烬</t>
+  </si>
+  <si>
+    <t>TileMud</t>
+  </si>
+  <si>
+    <t>地块泥浆</t>
+  </si>
+  <si>
+    <t>TileGlassBreak</t>
+  </si>
+  <si>
+    <t>地块玻璃碎裂</t>
+  </si>
+  <si>
+    <t>TileBrick</t>
+  </si>
+  <si>
+    <t>地块陶砖</t>
+  </si>
+  <si>
+    <t>TileFrozenSoil</t>
+  </si>
+  <si>
+    <t>地块冻土</t>
+  </si>
+  <si>
+    <t>Tile</t>
+  </si>
+  <si>
+    <t>地块土墙</t>
+  </si>
+  <si>
+    <t>TileThorn</t>
+  </si>
+  <si>
+    <t>地块荆棘</t>
+  </si>
+  <si>
+    <t>TileConduct</t>
+  </si>
+  <si>
+    <t>地块导电</t>
+  </si>
+  <si>
+    <t>EnemySpawn</t>
+  </si>
+  <si>
+    <t>敌人出生</t>
+  </si>
+  <si>
+    <t>EnemyKnockback</t>
+  </si>
+  <si>
+    <t>击退敌人</t>
+  </si>
+  <si>
+    <t>EnemtHit</t>
+  </si>
+  <si>
+    <t>敌人受击</t>
+  </si>
+  <si>
+    <t>EnemyDie</t>
+  </si>
+  <si>
+    <t>敌人死亡</t>
+  </si>
+  <si>
+    <t>PlayerPlant</t>
+  </si>
+  <si>
+    <t>玩家种植种子</t>
+  </si>
+  <si>
+    <t>PlayerHeal</t>
+  </si>
+  <si>
+    <t>玩家回血</t>
+  </si>
+  <si>
+    <t>StoryCGdrive</t>
+  </si>
+  <si>
+    <t>CG演出车行驶</t>
+  </si>
+  <si>
+    <t>StoryCGcardoor</t>
+  </si>
+  <si>
+    <t>CG演出开车门</t>
   </si>
 </sst>
 </file>
@@ -270,7 +432,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,14 +442,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -799,137 +967,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -940,21 +1108,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1277,7 +1448,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L128"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
@@ -1285,7 +1456,7 @@
     <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.3303571428571" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
   </cols>
@@ -1315,10 +1486,10 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="7"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1353,7 +1524,7 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1376,7 +1547,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1402,7 +1573,7 @@
       </c>
       <c r="K4"/>
     </row>
-    <row r="5" spans="2:11">
+    <row r="5" spans="1:12">
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
@@ -1420,7 +1591,7 @@
       </c>
       <c r="K5"/>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="1:12">
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
@@ -1432,7 +1603,7 @@
       <c r="J6"/>
       <c r="K6"/>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="1:12">
       <c r="B7" t="s">
         <v>25</v>
       </c>
@@ -1450,7 +1621,7 @@
       <c r="H7" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J7">
@@ -1458,7 +1629,7 @@
       </c>
       <c r="K7"/>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="1:12">
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1468,7 +1639,7 @@
       <c r="H8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>29</v>
       </c>
       <c r="J8">
@@ -1476,7 +1647,7 @@
       </c>
       <c r="K8"/>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="1:12">
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
@@ -1486,7 +1657,7 @@
       <c r="H9" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="J9">
@@ -1494,7 +1665,7 @@
       </c>
       <c r="K9"/>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="1:12">
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
@@ -1504,7 +1675,7 @@
       <c r="H10" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>33</v>
       </c>
       <c r="J10">
@@ -1512,7 +1683,7 @@
       </c>
       <c r="K10"/>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="1:12">
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
@@ -1522,7 +1693,7 @@
       <c r="H11" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>35</v>
       </c>
       <c r="J11">
@@ -1530,7 +1701,7 @@
       </c>
       <c r="K11"/>
     </row>
-    <row r="12" spans="2:11">
+    <row r="12" spans="1:12">
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
@@ -1540,7 +1711,7 @@
       <c r="H12" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J12">
@@ -1548,7 +1719,7 @@
       </c>
       <c r="K12"/>
     </row>
-    <row r="13" spans="2:11">
+    <row r="13" spans="1:12">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
@@ -1558,7 +1729,7 @@
       <c r="H13" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J13">
@@ -1566,7 +1737,7 @@
       </c>
       <c r="K13"/>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="1:12">
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1576,7 +1747,7 @@
       <c r="H14" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>41</v>
       </c>
       <c r="J14">
@@ -1584,7 +1755,7 @@
       </c>
       <c r="K14"/>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="1:12">
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -1594,7 +1765,7 @@
       <c r="H15" t="s">
         <v>42</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>43</v>
       </c>
       <c r="J15">
@@ -1602,7 +1773,7 @@
       </c>
       <c r="K15"/>
     </row>
-    <row r="16" spans="2:11">
+    <row r="16" spans="1:12">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1612,7 +1783,7 @@
       <c r="H16" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="7" t="s">
         <v>45</v>
       </c>
       <c r="J16">
@@ -1630,7 +1801,7 @@
       <c r="H17" t="s">
         <v>46</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="7" t="s">
         <v>47</v>
       </c>
       <c r="J17">
@@ -1638,7 +1809,7 @@
       </c>
       <c r="K17"/>
     </row>
-    <row r="18" spans="5:11">
+    <row r="18" spans="2:11">
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1707,7 +1878,7 @@
       </c>
       <c r="K21"/>
     </row>
-    <row r="22" spans="5:11">
+    <row r="22" spans="2:11">
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1776,7 +1947,7 @@
       </c>
       <c r="K25"/>
     </row>
-    <row r="26" spans="5:11">
+    <row r="26" spans="2:11">
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
@@ -1819,7 +1990,7 @@
       <c r="H28" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="8" t="s">
         <v>67</v>
       </c>
       <c r="J28">
@@ -1837,7 +2008,7 @@
       <c r="H29" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="8" t="s">
         <v>69</v>
       </c>
       <c r="J29">
@@ -1852,11 +2023,11 @@
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30"/>
-      <c r="I30" s="9"/>
+      <c r="I30" s="8"/>
       <c r="J30"/>
       <c r="K30"/>
     </row>
-    <row r="31" customFormat="1" spans="2:10">
+    <row r="31" customFormat="1" spans="2:11">
       <c r="B31" t="s">
         <v>70</v>
       </c>
@@ -1891,7 +2062,7 @@
       <c r="H32" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="8" t="s">
         <v>74</v>
       </c>
       <c r="J32">
@@ -1909,7 +2080,7 @@
       <c r="H33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I33" s="8" t="s">
         <v>76</v>
       </c>
       <c r="J33">
@@ -1924,8 +2095,15 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34"/>
-      <c r="I34" s="9"/>
-      <c r="J34"/>
+      <c r="H34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="J34">
+        <v>3</v>
+      </c>
       <c r="K34"/>
     </row>
     <row r="35" spans="2:11">
@@ -1935,8 +2113,15 @@
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35"/>
-      <c r="I35" s="9"/>
-      <c r="J35"/>
+      <c r="H35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
       <c r="K35"/>
     </row>
     <row r="36" spans="2:11">
@@ -1946,8 +2131,15 @@
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36"/>
-      <c r="I36" s="9"/>
-      <c r="J36"/>
+      <c r="H36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
       <c r="K36"/>
     </row>
     <row r="37" spans="2:11">
@@ -1957,8 +2149,15 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37"/>
-      <c r="I37" s="9"/>
-      <c r="J37"/>
+      <c r="H37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="J37">
+        <v>6</v>
+      </c>
       <c r="K37"/>
     </row>
     <row r="38" spans="2:11">
@@ -1968,8 +2167,15 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
-      <c r="I38" s="9"/>
-      <c r="J38"/>
+      <c r="H38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J38">
+        <v>7</v>
+      </c>
       <c r="K38"/>
     </row>
     <row r="39" spans="2:11">
@@ -1979,8 +2185,15 @@
       <c r="E39"/>
       <c r="F39"/>
       <c r="G39"/>
-      <c r="I39" s="9"/>
-      <c r="J39"/>
+      <c r="H39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J39">
+        <v>8</v>
+      </c>
       <c r="K39"/>
     </row>
     <row r="40" spans="2:11">
@@ -1990,8 +2203,15 @@
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40"/>
-      <c r="I40" s="9"/>
-      <c r="J40"/>
+      <c r="H40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="J40">
+        <v>9</v>
+      </c>
       <c r="K40"/>
     </row>
     <row r="41" spans="2:11">
@@ -2001,8 +2221,15 @@
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41"/>
-      <c r="I41" s="9"/>
-      <c r="J41"/>
+      <c r="H41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="J41">
+        <v>10</v>
+      </c>
       <c r="K41"/>
     </row>
     <row r="42" spans="2:11">
@@ -2012,8 +2239,15 @@
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42"/>
-      <c r="I42" s="9"/>
-      <c r="J42"/>
+      <c r="H42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J42">
+        <v>11</v>
+      </c>
       <c r="K42"/>
     </row>
     <row r="43" spans="2:11">
@@ -2023,8 +2257,15 @@
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43"/>
-      <c r="I43" s="9"/>
-      <c r="J43"/>
+      <c r="H43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="J43">
+        <v>12</v>
+      </c>
       <c r="K43"/>
     </row>
     <row r="44" spans="2:11">
@@ -2034,8 +2275,15 @@
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44"/>
-      <c r="I44" s="9"/>
-      <c r="J44"/>
+      <c r="H44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="J44">
+        <v>13</v>
+      </c>
       <c r="K44"/>
     </row>
     <row r="45" spans="2:11">
@@ -2045,17 +2293,31 @@
       <c r="E45"/>
       <c r="F45"/>
       <c r="G45"/>
-      <c r="I45" s="9"/>
-      <c r="J45"/>
+      <c r="H45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="J45">
+        <v>14</v>
+      </c>
       <c r="K45"/>
     </row>
     <row r="46" spans="2:11">
-      <c r="B46" s="5"/>
+      <c r="B46" s="11"/>
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46"/>
-      <c r="I46" s="5"/>
-      <c r="J46"/>
+      <c r="H46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="J46">
+        <v>15</v>
+      </c>
       <c r="K46"/>
     </row>
     <row r="47" spans="2:11">
@@ -2065,8 +2327,15 @@
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47"/>
-      <c r="I47" s="10"/>
-      <c r="J47"/>
+      <c r="H47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47">
+        <v>16</v>
+      </c>
       <c r="K47"/>
     </row>
     <row r="48" spans="2:11">
@@ -2076,8 +2345,15 @@
       <c r="E48"/>
       <c r="F48"/>
       <c r="G48"/>
-      <c r="I48" s="10"/>
-      <c r="J48"/>
+      <c r="H48" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="J48">
+        <v>17</v>
+      </c>
       <c r="K48"/>
     </row>
     <row r="49" spans="2:11">
@@ -2087,8 +2363,15 @@
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49"/>
-      <c r="I49" s="10"/>
-      <c r="J49"/>
+      <c r="H49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J49">
+        <v>18</v>
+      </c>
       <c r="K49"/>
     </row>
     <row r="50" spans="2:11">
@@ -2098,8 +2381,15 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50"/>
-      <c r="I50" s="10"/>
-      <c r="J50"/>
+      <c r="H50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J50">
+        <v>19</v>
+      </c>
       <c r="K50"/>
     </row>
     <row r="51" spans="2:11">
@@ -2109,8 +2399,15 @@
       <c r="E51"/>
       <c r="F51"/>
       <c r="G51"/>
-      <c r="I51" s="10"/>
-      <c r="J51"/>
+      <c r="H51" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="J51">
+        <v>20</v>
+      </c>
       <c r="K51"/>
     </row>
     <row r="52" spans="2:11">
@@ -2120,8 +2417,15 @@
       <c r="E52"/>
       <c r="F52"/>
       <c r="G52"/>
-      <c r="I52" s="10"/>
-      <c r="J52"/>
+      <c r="H52" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J52">
+        <v>21</v>
+      </c>
       <c r="K52"/>
     </row>
     <row r="53" spans="2:11">
@@ -2131,8 +2435,15 @@
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53"/>
-      <c r="I53" s="10"/>
-      <c r="J53"/>
+      <c r="H53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="J53">
+        <v>22</v>
+      </c>
       <c r="K53"/>
     </row>
     <row r="54" spans="2:11">
@@ -2142,8 +2453,15 @@
       <c r="E54"/>
       <c r="F54"/>
       <c r="G54"/>
-      <c r="I54" s="10"/>
-      <c r="J54"/>
+      <c r="H54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="J54">
+        <v>23</v>
+      </c>
       <c r="K54"/>
     </row>
     <row r="55" spans="2:11">
@@ -2153,8 +2471,15 @@
       <c r="E55"/>
       <c r="F55"/>
       <c r="G55"/>
-      <c r="I55" s="10"/>
-      <c r="J55"/>
+      <c r="H55" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="J55">
+        <v>24</v>
+      </c>
       <c r="K55"/>
     </row>
     <row r="56" spans="2:11">
@@ -2164,8 +2489,15 @@
       <c r="E56"/>
       <c r="F56"/>
       <c r="G56"/>
-      <c r="I56" s="10"/>
-      <c r="J56"/>
+      <c r="H56" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="J56">
+        <v>25</v>
+      </c>
       <c r="K56"/>
     </row>
     <row r="57" spans="2:11">
@@ -2175,8 +2507,15 @@
       <c r="E57"/>
       <c r="F57"/>
       <c r="G57"/>
-      <c r="I57" s="10"/>
-      <c r="J57"/>
+      <c r="H57" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="J57">
+        <v>26</v>
+      </c>
       <c r="K57"/>
     </row>
     <row r="58" spans="2:11">
@@ -2186,9 +2525,15 @@
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58"/>
-      <c r="H58"/>
-      <c r="I58"/>
-      <c r="J58"/>
+      <c r="H58" t="s">
+        <v>125</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="J58">
+        <v>27</v>
+      </c>
       <c r="K58"/>
     </row>
     <row r="59" spans="2:11">
@@ -2198,9 +2543,15 @@
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59"/>
+      <c r="H59" t="s">
+        <v>127</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="J59">
+        <v>28</v>
+      </c>
       <c r="K59"/>
     </row>
     <row r="60" spans="2:11">
@@ -2210,9 +2561,15 @@
       <c r="E60"/>
       <c r="F60"/>
       <c r="G60"/>
-      <c r="H60"/>
-      <c r="I60"/>
-      <c r="J60"/>
+      <c r="H60" t="s">
+        <v>129</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="J60">
+        <v>29</v>
+      </c>
       <c r="K60"/>
     </row>
     <row r="61" spans="2:11">

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -420,6 +420,18 @@
   </si>
   <si>
     <t>CG演出开车门</t>
+  </si>
+  <si>
+    <t>BgmMain</t>
+  </si>
+  <si>
+    <t>主题bgm</t>
+  </si>
+  <si>
+    <t>BgmAscensio</t>
+  </si>
+  <si>
+    <t>升华bgm</t>
   </si>
 </sst>
 </file>
@@ -2579,9 +2591,15 @@
       <c r="E61"/>
       <c r="F61"/>
       <c r="G61"/>
-      <c r="H61"/>
-      <c r="I61"/>
-      <c r="J61"/>
+      <c r="H61" t="s">
+        <v>131</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J61">
+        <v>30</v>
+      </c>
       <c r="K61"/>
     </row>
     <row r="62" spans="2:11">
@@ -2591,9 +2609,15 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62"/>
+      <c r="H62" t="s">
+        <v>133</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J62">
+        <v>31</v>
+      </c>
       <c r="K62"/>
     </row>
     <row r="63" spans="2:11">

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="137">
   <si>
     <t>##var</t>
   </si>
@@ -432,6 +432,12 @@
   </si>
   <si>
     <t>升华bgm</t>
+  </si>
+  <si>
+    <t>UIBagSlide</t>
+  </si>
+  <si>
+    <t>UI背包按钮滑动</t>
   </si>
 </sst>
 </file>
@@ -2627,9 +2633,15 @@
       <c r="E63"/>
       <c r="F63"/>
       <c r="G63"/>
-      <c r="H63"/>
-      <c r="I63"/>
-      <c r="J63"/>
+      <c r="H63" t="s">
+        <v>135</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J63">
+        <v>32</v>
+      </c>
       <c r="K63"/>
     </row>
     <row r="64" spans="2:11">

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="149">
   <si>
     <t>##var</t>
   </si>
@@ -441,6 +441,12 @@
   </si>
   <si>
     <t>UI背包按钮滑动</t>
+  </si>
+  <si>
+    <t>PlayerHurt</t>
+  </si>
+  <si>
+    <t>玩家受伤</t>
   </si>
   <si>
     <t>dso.DialogType</t>
@@ -1495,7 +1501,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
@@ -2701,42 +2707,42 @@
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65"/>
-      <c r="H65"/>
-      <c r="I65"/>
-      <c r="J65"/>
+      <c r="H65" t="s">
+        <v>138</v>
+      </c>
+      <c r="I65" t="s">
+        <v>139</v>
+      </c>
+      <c r="J65">
+        <v>33</v>
+      </c>
       <c r="K65"/>
     </row>
     <row r="66" spans="2:11">
-      <c r="B66" t="s">
-        <v>138</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66" t="s">
-        <v>20</v>
-      </c>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
       <c r="F66"/>
       <c r="G66"/>
-      <c r="H66" t="s">
-        <v>139</v>
-      </c>
-      <c r="I66" s="11" t="s">
+      <c r="H66"/>
+      <c r="I66" s="11"/>
+      <c r="J66"/>
+      <c r="K66"/>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" t="s">
         <v>140</v>
       </c>
-      <c r="J66">
+      <c r="C67">
         <v>0</v>
       </c>
-      <c r="K66"/>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67"/>
-      <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67"/>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>20</v>
+      </c>
       <c r="F67"/>
       <c r="G67"/>
       <c r="H67" t="s">
@@ -2746,7 +2752,7 @@
         <v>142</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67"/>
     </row>
@@ -2764,7 +2770,7 @@
         <v>144</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68"/>
     </row>
@@ -2782,7 +2788,7 @@
         <v>146</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K69"/>
     </row>
@@ -2793,9 +2799,15 @@
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70"/>
-      <c r="H70"/>
-      <c r="I70"/>
-      <c r="J70"/>
+      <c r="H70" t="s">
+        <v>147</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="J70">
+        <v>3</v>
+      </c>
       <c r="K70"/>
     </row>
     <row r="71" spans="2:11">
@@ -3494,6 +3506,18 @@
       <c r="J128"/>
       <c r="K128"/>
     </row>
+    <row r="129" spans="2:11">
+      <c r="B129"/>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="H129"/>
+      <c r="I129"/>
+      <c r="J129"/>
+      <c r="K129"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="151">
   <si>
     <t>##var</t>
   </si>
@@ -447,6 +447,12 @@
   </si>
   <si>
     <t>玩家受伤</t>
+  </si>
+  <si>
+    <t>PlayerDash</t>
+  </si>
+  <si>
+    <t>玩家冲刺</t>
   </si>
   <si>
     <t>dso.DialogType</t>
@@ -1501,7 +1507,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
@@ -2725,42 +2731,42 @@
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66" s="11"/>
-      <c r="J66"/>
+      <c r="H66" t="s">
+        <v>140</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="J66">
+        <v>34</v>
+      </c>
       <c r="K66"/>
     </row>
     <row r="67" spans="2:11">
-      <c r="B67" t="s">
-        <v>140</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
-        <v>20</v>
-      </c>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
       <c r="F67"/>
       <c r="G67"/>
-      <c r="H67" t="s">
-        <v>141</v>
-      </c>
-      <c r="I67" s="11" t="s">
+      <c r="H67"/>
+      <c r="I67" s="11"/>
+      <c r="J67"/>
+      <c r="K67"/>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" t="s">
         <v>142</v>
       </c>
-      <c r="J67">
+      <c r="C68">
         <v>0</v>
       </c>
-      <c r="K67"/>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68"/>
-      <c r="C68"/>
-      <c r="D68"/>
-      <c r="E68"/>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>20</v>
+      </c>
       <c r="F68"/>
       <c r="G68"/>
       <c r="H68" t="s">
@@ -2770,7 +2776,7 @@
         <v>144</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68"/>
     </row>
@@ -2788,7 +2794,7 @@
         <v>146</v>
       </c>
       <c r="J69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69"/>
     </row>
@@ -2806,7 +2812,7 @@
         <v>148</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K70"/>
     </row>
@@ -2817,9 +2823,15 @@
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71"/>
+      <c r="H71" t="s">
+        <v>149</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="J71">
+        <v>3</v>
+      </c>
       <c r="K71"/>
     </row>
     <row r="72" spans="2:11">
@@ -3518,6 +3530,18 @@
       <c r="J129"/>
       <c r="K129"/>
     </row>
+    <row r="130" spans="2:11">
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="I130"/>
+      <c r="J130"/>
+      <c r="K130"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/ConfigWorkspace/Data/__enums__.xlsx
+++ b/ConfigWorkspace/Data/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="23120" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="153">
   <si>
     <t>##var</t>
   </si>
@@ -447,6 +447,18 @@
   </si>
   <si>
     <t>玩家受伤</t>
+  </si>
+  <si>
+    <t>PlayerGO</t>
+  </si>
+  <si>
+    <t>玩家冲刺</t>
+  </si>
+  <si>
+    <t>PlayerDie</t>
+  </si>
+  <si>
+    <t>死亡失败结算</t>
   </si>
   <si>
     <t>dso.DialogType</t>
@@ -496,12 +508,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -510,6 +516,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1162,22 +1174,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -1501,8 +1513,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L129"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:L131"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
@@ -1510,7 +1522,7 @@
     <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.3303571428571" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
   </cols>
@@ -1540,10 +1552,10 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="7"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1578,7 +1590,7 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1601,7 +1613,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1627,7 +1639,7 @@
       </c>
       <c r="K4"/>
     </row>
-    <row r="5" spans="2:11">
+    <row r="5" spans="1:12">
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
@@ -1645,7 +1657,7 @@
       </c>
       <c r="K5"/>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="1:12">
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
@@ -1657,7 +1669,7 @@
       <c r="J6"/>
       <c r="K6"/>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="1:12">
       <c r="B7" t="s">
         <v>25</v>
       </c>
@@ -1675,7 +1687,7 @@
       <c r="H7" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J7">
@@ -1683,7 +1695,7 @@
       </c>
       <c r="K7"/>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="1:12">
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1693,7 +1705,7 @@
       <c r="H8" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>29</v>
       </c>
       <c r="J8">
@@ -1701,7 +1713,7 @@
       </c>
       <c r="K8"/>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="1:12">
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
@@ -1711,7 +1723,7 @@
       <c r="H9" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="J9">
@@ -1719,7 +1731,7 @@
       </c>
       <c r="K9"/>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="1:12">
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
@@ -1729,7 +1741,7 @@
       <c r="H10" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>33</v>
       </c>
       <c r="J10">
@@ -1737,7 +1749,7 @@
       </c>
       <c r="K10"/>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="1:12">
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
@@ -1747,7 +1759,7 @@
       <c r="H11" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>35</v>
       </c>
       <c r="J11">
@@ -1755,7 +1767,7 @@
       </c>
       <c r="K11"/>
     </row>
-    <row r="12" spans="2:11">
+    <row r="12" spans="1:12">
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
@@ -1765,7 +1777,7 @@
       <c r="H12" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J12">
@@ -1773,7 +1785,7 @@
       </c>
       <c r="K12"/>
     </row>
-    <row r="13" spans="2:11">
+    <row r="13" spans="1:12">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
@@ -1783,7 +1795,7 @@
       <c r="H13" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J13">
@@ -1791,7 +1803,7 @@
       </c>
       <c r="K13"/>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="1:12">
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1801,7 +1813,7 @@
       <c r="H14" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>41</v>
       </c>
       <c r="J14">
@@ -1809,7 +1821,7 @@
       </c>
       <c r="K14"/>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="1:12">
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -1819,7 +1831,7 @@
       <c r="H15" t="s">
         <v>42</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>43</v>
       </c>
       <c r="J15">
@@ -1827,7 +1839,7 @@
       </c>
       <c r="K15"/>
     </row>
-    <row r="16" spans="2:11">
+    <row r="16" spans="1:12">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1837,7 +1849,7 @@
       <c r="H16" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="7" t="s">
         <v>45</v>
       </c>
       <c r="J16">
@@ -1855,7 +1867,7 @@
       <c r="H17" t="s">
         <v>46</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="7" t="s">
         <v>47</v>
       </c>
       <c r="J17">
@@ -1863,7 +1875,7 @@
       </c>
       <c r="K17"/>
     </row>
-    <row r="18" spans="5:11">
+    <row r="18" spans="2:11">
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1932,7 +1944,7 @@
       </c>
       <c r="K21"/>
     </row>
-    <row r="22" spans="5:11">
+    <row r="22" spans="2:11">
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -2047,7 +2059,7 @@
       <c r="H28" t="s">
         <v>66</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="8" t="s">
         <v>67</v>
       </c>
       <c r="J28">
@@ -2065,7 +2077,7 @@
       <c r="H29" t="s">
         <v>68</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="8" t="s">
         <v>69</v>
       </c>
       <c r="J29">
@@ -2083,7 +2095,7 @@
       <c r="H30" t="s">
         <v>70</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="8" t="s">
         <v>71</v>
       </c>
       <c r="J30">
@@ -2091,7 +2103,7 @@
       </c>
       <c r="K30"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:11">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -2118,7 +2130,7 @@
       <c r="H32" t="s">
         <v>26</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="8" t="s">
         <v>73</v>
       </c>
       <c r="J32">
@@ -2136,7 +2148,7 @@
       <c r="H33" t="s">
         <v>74</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I33" s="8" t="s">
         <v>75</v>
       </c>
       <c r="J33">
@@ -2154,7 +2166,7 @@
       <c r="H34" t="s">
         <v>76</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="I34" s="9" t="s">
         <v>77</v>
       </c>
       <c r="J34">
@@ -2172,7 +2184,7 @@
       <c r="H35" t="s">
         <v>78</v>
       </c>
-      <c r="I35" s="10" t="s">
+      <c r="I35" s="9" t="s">
         <v>79</v>
       </c>
       <c r="J35">
@@ -2190,7 +2202,7 @@
       <c r="H36" t="s">
         <v>80</v>
       </c>
-      <c r="I36" s="10" t="s">
+      <c r="I36" s="9" t="s">
         <v>81</v>
       </c>
       <c r="J36">
@@ -2361,7 +2373,7 @@
       <c r="K45"/>
     </row>
     <row r="46" spans="2:11">
-      <c r="B46" s="5"/>
+      <c r="B46" s="10"/>
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46"/>
@@ -2674,7 +2686,7 @@
       <c r="H63" t="s">
         <v>134</v>
       </c>
-      <c r="I63" s="9" t="s">
+      <c r="I63" s="8" t="s">
         <v>135</v>
       </c>
       <c r="J63">
@@ -2725,34 +2737,32 @@
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66" s="11"/>
-      <c r="J66"/>
+      <c r="H66" t="s">
+        <v>140</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="J66">
+        <v>34</v>
+      </c>
       <c r="K66"/>
     </row>
     <row r="67" spans="2:11">
-      <c r="B67" t="s">
-        <v>140</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
-        <v>20</v>
-      </c>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
       <c r="F67"/>
       <c r="G67"/>
       <c r="H67" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K67"/>
     </row>
@@ -2763,22 +2773,24 @@
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68"/>
-      <c r="H68" t="s">
-        <v>143</v>
-      </c>
-      <c r="I68" s="11" t="s">
+      <c r="H68"/>
+      <c r="I68" s="11"/>
+      <c r="J68"/>
+      <c r="K68"/>
+    </row>
+    <row r="69" spans="2:11">
+      <c r="B69" t="s">
         <v>144</v>
       </c>
-      <c r="J68">
-        <v>1</v>
-      </c>
-      <c r="K68"/>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69"/>
-      <c r="C69"/>
-      <c r="D69"/>
-      <c r="E69"/>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>20</v>
+      </c>
       <c r="F69"/>
       <c r="G69"/>
       <c r="H69" t="s">
@@ -2788,7 +2800,7 @@
         <v>146</v>
       </c>
       <c r="J69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K69"/>
     </row>
@@ -2806,7 +2818,7 @@
         <v>148</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K70"/>
     </row>
@@ -2817,9 +2829,15 @@
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71"/>
+      <c r="H71" t="s">
+        <v>149</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
       <c r="K71"/>
     </row>
     <row r="72" spans="2:11">
@@ -2829,9 +2847,15 @@
       <c r="E72"/>
       <c r="F72"/>
       <c r="G72"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
+      <c r="H72" t="s">
+        <v>151</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="J72">
+        <v>3</v>
+      </c>
       <c r="K72"/>
     </row>
     <row r="73" spans="2:11">
@@ -3518,6 +3542,30 @@
       <c r="J129"/>
       <c r="K129"/>
     </row>
+    <row r="130" spans="2:11">
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="I130"/>
+      <c r="J130"/>
+      <c r="K130"/>
+    </row>
+    <row r="131" spans="2:11">
+      <c r="B131"/>
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="H131"/>
+      <c r="I131"/>
+      <c r="J131"/>
+      <c r="K131"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
